--- a/docs/upstream/manual-regression-checklist-qa.xlsx
+++ b/docs/upstream/manual-regression-checklist-qa.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Dedup log" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Checklist'!$A$1:$I$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Checklist'!$A$1:$I$138</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dedup log'!$A$1:$C$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I128"/>
+  <dimension ref="A1:I138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -763,12 +763,14 @@
       <c r="F8" s="2" t="inlineStr">
         <is>
           <t>1. Load workspace home and a workflow.
-2. Check logos, favicon, API key labels, and docs title.</t>
+2. Check logos, favicon, API key labels, and docs title.
+3. Open the Slack setup wizard and the Slack block auth method.
+4. Open a deploy-modal API sample and find the billing header.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Arena logos/favicon present. Labels say Arena key (not Sim key). Docs title is P2 Agents Docs.</t>
+          <t>Arena logos/favicon present. Labels say Arena key (not Sim key). Docs title is P2 Agents Docs. Slack says Arena Bot, Arena app, and Arena Workflow Bot. The billing header remains X-Sim-Email.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
@@ -795,18 +797,18 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Sidebar Usage; Billing admins only</t>
+          <t>Usage for every member; Billing admins only; Insights gated</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1. As org admin: open sidebar / settings and look for Usage and Billing.
-2. As non-admin member: repeat.</t>
+          <t>1. As a member who cannot manage billing, open Subscription → Usage and try Billing.
+2. As an org admin, open Billing and Organization → Insights.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Usage is visible. Billing is visible only to org admins; non-admins cannot open billing.</t>
+          <t>Usage (/settings/arena-usage) opens for every member and shows remaining credits. A non-admin who opens Billing lands on Usage. /settings/arena-billing shows the billing panel, not an empty heading. Insights (/settings/usage) stays limited to org admins on enterprise, or the self-hosted usage-monitoring flag.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
@@ -833,17 +835,19 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Back to Arena agents</t>
+          <t>Default theme is light; dark editor popovers stay readable</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1. From the Sim/Arena agent shell, click Back to Arena agents.</t>
+          <t>1. Sign in as a user with no saved theme (or clear the saved theme) and reload.
+2. Switch to dark mode.
+3. In the workflow editor, open the env-var dropdown, tag dropdown, and messages-input popover.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Browser returns to the Arena hub agents URL.</t>
+          <t>The first load is light. Dark mode still applies when chosen. Those popovers use dark surfaces and readable text.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
@@ -870,18 +874,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Help menu stays hidden</t>
+          <t>Back to Arena agents</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1. Inspect workspace sidebar footer / more menu.
-2. Confirm there is no standalone Help menu entry (help lives under Settings if at all).</t>
+          <t>1. From the Sim/Arena agent shell, click Back to Arena agents.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>No dedicated Help menu chrome in the sidebar. Intentionally-off Arena behaviour holds.</t>
+          <t>Browser returns to the Arena hub agents URL.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
@@ -908,18 +911,18 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Home empty state has no CreditsChip</t>
+          <t>Help menu stays hidden</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1. Open workspace home with an empty chat surface.
-2. Look for a CreditsChip on the empty state.</t>
+          <t>1. Inspect workspace sidebar footer / more menu.
+2. Confirm there is no standalone Help menu entry (help lives under Settings if at all).</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>CreditsChip is absent. Billing remains under Usage / org-admin paths only.</t>
+          <t>No dedicated Help menu chrome in the sidebar. Intentionally-off Arena behaviour holds.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
@@ -936,67 +939,67 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>Identity and shell</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Home empty state has no CreditsChip</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1. Open workspace home with an empty chat surface.
+2. Look for a CreditsChip on the empty state.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>CreditsChip is absent. Billing remains under Usage / org-admin paths only.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14" ht="90" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>1. Customized — Sim behavior Arena changed</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
           <t>Sign-in and OAuth</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Unauthenticated traffic → Arena SSO resume</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>1. Open an agent URL while signed out.
 2. Complete Arena SSO.
 3. Confirm return into Sim.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Redirect goes to Arena SSO. After login, session resumes back into the original Sim/agent path.</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>1. Customized — Sim behavior Arena changed</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Sign-in and OAuth</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Hub origins credentialed APIs; legal → Arena URLs</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1. From an allowlisted hub origin, call a credentialed API with cookies.
-2. Open legal/privacy/terms links from the product.</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Hub credentialed calls succeed (CORS/cookies). Legal pages redirect to Arena URLs.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
@@ -1023,18 +1026,18 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Session create supersedes Starter when paid is active</t>
+          <t>Hub origins credentialed APIs; legal → Arena URLs</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1. Org on Starter upgrades to a paid Arena plan (or already has paid active).
-2. Trigger session create / refresh billing entitlements.</t>
+          <t>1. From an allowlisted hub origin, call a credentialed API with cookies.
+2. Open legal/privacy/terms links from the product.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Paid plan supersedes Starter. Starter is no longer the blocking entitlement.</t>
+          <t>Hub credentialed calls succeed (CORS/cookies). Legal pages redirect to Arena URLs.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr"/>
@@ -1061,57 +1064,57 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>Session create supersedes Starter when paid is active</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1. Org on Starter upgrades to a paid Arena plan (or already has paid active).
+2. Trigger session create / refresh billing entitlements.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Paid plan supersedes Starter. Starter is no longer the blocking entitlement.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>1. Customized — Sim behavior Arena changed</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Sign-in and OAuth</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>Zoom user app and Zoom admin app connect</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>1. Connect Zoom user OAuth.
 2. Connect Zoom admin app (admin scopes).
 3. Spot-check recordings/transcripts access if credentials allow.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Both apps connect successfully. Admin scopes available for recordings/transcripts.</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17" ht="90" customHeight="1">
-      <c r="A17" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>1. Customized — Sim behavior Arena changed</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Sign-in and OAuth</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Facebook Ads and Bing Ads OAuth connect</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1. Start Facebook Ads OAuth and complete consent.
-2. Start Bing Ads OAuth and complete consent.</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Both OAuth flows complete with expected scopes. Credentials appear as connected.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
@@ -1138,18 +1141,18 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>HubSpot shared-portal alias resolves credential</t>
+          <t>Facebook Ads and Bing Ads OAuth connect</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1. Use a HubSpot shared-portal alias in a workflow or credential picker.
-2. Run a simple HubSpot read.</t>
+          <t>1. Start Facebook Ads OAuth and complete consent.
+2. Start Bing Ads OAuth and complete consent.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>The alias resolves to the correct credential; the read succeeds against the expected portal.</t>
+          <t>Both OAuth flows complete with expected scopes. Credentials appear as connected.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
@@ -1166,7 +1169,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Deployed chat</t>
+          <t>Sign-in and OAuth</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1176,18 +1179,18 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Landing, welcome CTAs, theme, department</t>
+          <t>HubSpot shared-portal alias resolves credential</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1. Open a deployed agent public URL (ArenaDeployedChat).
-2. Inspect landing, welcome CTAs, theme, department label.</t>
+          <t>1. Use a HubSpot shared-portal alias in a workflow or credential picker.
+2. Run a simple HubSpot read.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Landing, welcome CTAs, theme, and department label all render correctly.</t>
+          <t>The alias resolves to the correct credential; the read succeeds against the expected portal.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
@@ -1214,19 +1217,18 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Streamed reply with charts, images, thinking/tool segments</t>
+          <t>Landing, welcome CTAs, theme, department</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1. Send a message that yields a streamed reply.
-2. If the workflow enables them, confirm thinking / tool-call segments.
-3. Trigger a chart and a generated image; reuse the image if UI allows.</t>
+          <t>1. Open a deployed agent public URL (ArenaDeployedChat).
+2. Inspect landing, welcome CTAs, theme, department label.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Reply streams. Thinking/tool-call segments show when enabled. ECharts charts render. Images appear and can be reused.</t>
+          <t>Landing, welcome CTAs, theme, and department label all render correctly.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
@@ -1253,174 +1255,177 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>Streamed reply with charts, images, thinking/tool segments</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>1. Send a message that yields a streamed reply.
+2. If the workflow enables them, confirm thinking / tool-call segments.
+3. Trigger a chart and a generated image, including a base64 or data-URL image. Reuse the image.
+4. Refresh deployed chat and the workflow builder chat panel.</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Reply streams. Thinking/tool-call segments show when enabled. ECharts charts render. Images appear and can be reused. Raw base64 is not shown as message text. The image still renders after refresh.</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22" ht="90" customHeight="1">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>1. Customized — Sim behavior Arena changed</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Deployed chat</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Visitor without a workspace seat still runs</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a deployed chat as a user who is allowed on the agent but has no seat in that workflow’s workspace.
+2. Send a message on a workflow that reads workspace secrets.</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>The visitor gets a reply. The run does not fail on membership or a stale owner.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23" ht="90" customHeight="1">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>1. Customized — Sim behavior Arena changed</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Deployed chat</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
           <t>Builder panel Launch opens the deployed chat</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>1. Open a workflow deployed as chat. Confirm the right panel shows Launch (lightning) beside Run.
 2. Click Launch. Confirm the deployed chat opens with fromControlBar=true.
 3. Open a workflow that is not deployed as chat or app.
-4. Click Run on the deployed workflow and run the canvas.</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Launch is present only for a chat or app deployment and opens that deployment. It is absent otherwise. Run still executes the workflow in the builder and is not renamed.</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22" ht="90" customHeight="1">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
+4. Click Run on the deployed workflow and run the canvas.
+5. Narrow the panel until Deploy, Launch, and Run share a short row. On home, select a long Local model name.</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Launch is present only for a chat or app deployment and opens that deployment. It is absent otherwise. Run still executes the workflow in the builder and is not renamed. Deploy, Launch, and Run stay on one row without overlapping. The model name truncates instead of stretching the composer.</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24" ht="90" customHeight="1">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>1. Customized — Sim behavior Arena changed</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Deployed chat</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Threads: create, switch, rename, reload history</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>1. Create a new thread; send a message.
 2. Switch threads; rename one; reload the page.
 3. Confirm history returns without needing webhook/schedule.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Create/switch/rename work. History persists after reload. No webhook or schedule required for history.</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23" ht="90" customHeight="1">
-      <c r="A23" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25" ht="90" customHeight="1">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>1. Customized — Sim behavior Arena changed</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Deployed chat</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Golden queries load and insert</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>1. Open a deployed agent configured with golden queries.
 2. Load the list and insert one into the composer.
 3. Send it.</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>Golden queries load and insert into the composer; send works.</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24" ht="90" customHeight="1">
-      <c r="A24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>1. Customized — Sim behavior Arena changed</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Deployed chat</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Feedback submit and feedback view</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1. Submit prompt/reply feedback from deployed chat.
-2. Open the feedback view.</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Feedback submits successfully and is visible in the feedback view.</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25" ht="90" customHeight="1">
-      <c r="A25" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>1. Customized — Sim behavior Arena changed</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Deployed chat</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Knowledge references survive refresh</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>1. Get a reply that includes knowledge references.
-2. Refresh the page.</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Knowledge references remain on the reply after refresh.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
@@ -1447,94 +1452,95 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
+          <t>Feedback submit and feedback view</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>1. Submit prompt/reply feedback from deployed chat.
+2. Open the feedback view for a reply that includes a chart.</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Feedback submits successfully and is visible in the feedback view. The chart renders as a chart, not raw option JSON.</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="90" customHeight="1">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>1. Customized — Sim behavior Arena changed</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Deployed chat</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Knowledge references survive refresh</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>1. Get a reply that includes knowledge references.
+2. Refresh the page.</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Knowledge references remain on the reply after refresh.</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28" ht="90" customHeight="1">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>1. Customized — Sim behavior Arena changed</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Deployed chat</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>Inactive or unauthorized chat → error, no junk log</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>1. Note execution-log / run count for the deployment.
 2. Open an inactive or unauthorized chat URL and attempt a send.
 3. Re-check the log count.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Client gets an error (403 for inactive/unauthorized). No new junk execution log row is written.</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27" ht="90" customHeight="1">
-      <c r="A27" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>1. Customized — Sim behavior Arena changed</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Deployed chat</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Voice controls stay absent</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>1. Inspect deployed chat chrome for voice/mic controls.</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>No voice controls are present on deployed chat.</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28" ht="90" customHeight="1">
-      <c r="A28" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>1. Customized — Sim behavior Arena changed</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Workspace chat and Local/Cloud copilot</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Workspace home chat streams</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>1. On workspace home, send a chat message.
-2. Watch stream, theme, charts if applicable, and usage attribution.</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Reply streams. Theme/charts work when produced. Usage attribution still recorded.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
@@ -1551,7 +1557,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Workspace chat and Local/Cloud copilot</t>
+          <t>Deployed chat</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1561,18 +1567,17 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Allowlisted users see Local/Cloud switch</t>
+          <t>Voice controls stay absent</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1. Sign in as a user with hasAccess (not localOnly).
-2. Check workspace home and the workflow Copilot tab.</t>
+          <t>1. Inspect deployed chat chrome for voice/mic controls.</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Local / Cloud switch is visible on home and on the workflow Copilot tab.</t>
+          <t>No voice controls are present on deployed chat.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
@@ -1599,18 +1604,18 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Local uses Arena Copilot; Cloud uses Mothership</t>
+          <t>Workspace home chat streams</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1. With COPILOT_API_KEY configured, send on Local.
-2. Switch to Cloud and send.</t>
+          <t>1. On workspace home, send a chat message.
+2. Watch stream, theme, charts if applicable, and usage attribution.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Local returns an Arena Copilot (local model) reply. Cloud uses Mothership.</t>
+          <t>Reply streams. Theme/charts work when produced. Usage attribution still recorded.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -1637,18 +1642,18 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Local model picker persists; session memory inspector</t>
+          <t>Allowlisted users see Local/Cloud switch</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1. Change the Local model picker; reload.
-2. On a longer Local thread, open the session memory inspector if shown.</t>
+          <t>1. Sign in as a user with hasAccess (not localOnly).
+2. Check workspace home and the workflow Copilot tab.</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Picker selection persists as the user default. Session memory inspector appears on longer Local threads.</t>
+          <t>Local / Cloud switch is visible on home and on the workflow Copilot tab.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
@@ -1675,974 +1680,979 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>Local uses Arena Copilot; Cloud uses Mothership</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>1. With COPILOT_API_KEY configured, send on Local.
+2. Switch to Cloud and send.</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Local returns an Arena Copilot (local model) reply. Cloud uses Mothership.</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33" ht="90" customHeight="1">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>1. Customized — Sim behavior Arena changed</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Workspace chat and Local/Cloud copilot</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Local model picker persists; session memory inspector</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>1. Change the Local model picker; reload.
+2. On a longer Local thread, open the session memory inspector if shown.
+3. Confirm Claude Fable 5.1, GPT-6 Astra, and GPT-5.5 are listed. Send with one of them.</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Picker selection persists as the user default. Session memory inspector appears on longer Local threads. Those three models are listed and the chosen one returns a reply.</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34" ht="90" customHeight="1">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>1. Customized — Sim behavior Arena changed</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Workspace chat and Local/Cloud copilot</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Second Cloud turn and Local recovery do not show Run not found</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>1. On Cloud, finish one turn, leave the chat idle, then send again.
+2. On Local, start a turn that reconnects (refresh mid-thread or send after idle) and confirm the backend stays Local.</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Both turns complete. The user does not see “Run not found”. The Local turn is not reattached to the Cloud worker.</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35" ht="90" customHeight="1">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>1. Customized — Sim behavior Arena changed</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Workspace chat and Local/Cloud copilot</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Finished Copilot reply does not turn asterisks into bold on scroll</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>1. Get a Copilot reply that contains ordinary * characters or unfinished markdown.
+2. Wait until the reply has finished, then scroll the thread away and back.</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>The finished text stays as it streamed. Scrolling does not turn those characters into bold.</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36" ht="90" customHeight="1">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>1. Customized — Sim behavior Arena changed</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Workspace chat and Local/Cloud copilot</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Fetch-and-send sequence is canvas blocks, not Agent tools</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>1. Ask Copilot: today’s calendar, unread Gmail, Slack messages, then a written briefing.
+2. Also ask for a daily time trigger.
+3. Inspect the canvas block types and the Agent tools list.</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>The canvas has google_calendar_v2, gmail_v2, and slack as their own blocks in that order. Those integrations are not Agent tools. The daily trigger is a schedule block, not schedule_trigger.</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37" ht="90" customHeight="1">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>1. Customized — Sim behavior Arena changed</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Workspace chat and Local/Cloud copilot</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Copilot HTML file opens as a complete page</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>1. Ask Copilot to create an HTML page.
+2. Open the saved file.</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>The file opens as a complete page. The chat does not dump a truncated tag soup in place of the file.</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38" ht="90" customHeight="1">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>1. Customized — Sim behavior Arena changed</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Workspace chat and Local/Cloud copilot</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>Local-only users stay on Local without the switch</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as a localOnly allowlisted user.
 2. Open home and workflow Copilot.
 3. Send a message (even if a stale Cloud preference exists).</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>No Local/Cloud switch. Sends stay on Local.</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33" ht="90" customHeight="1">
-      <c r="A33" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39" ht="90" customHeight="1">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>1. Customized — Sim behavior Arena changed</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>Workspace chat and Local/Cloud copilot</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Copilot images/files land on Arena ledger</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>1. From Copilot, generate an image and create a file on Local.
 2. Open Usage / ledger.</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>Image/file usage appears on the Arena ledger for the Local turns.</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34" ht="90" customHeight="1">
-      <c r="A34" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40" ht="90" customHeight="1">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>1. Customized — Sim behavior Arena changed</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Workspace chat and Local/Cloud copilot</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Floating workflow chat streams chart/image</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>1. Open floating workflow chat.
 2. Run a prompt that produces chart and/or image output.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>Run streams; chart and image output render in the floating chat.</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35" ht="90" customHeight="1">
-      <c r="A35" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="90" customHeight="1">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>1. Customized — Sim behavior Arena changed</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>Workspace chat and Local/Cloud copilot</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Deploy-modal chat preview matches deployed agent</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>1. Open deploy modal chat preview for an agent.
 2. Compare theming/welcome behaviour to the live deployed URL.</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>Preview matches the deployed agent experience (theme, welcome, basic send).</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36" ht="90" customHeight="1">
-      <c r="A36" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42" ht="90" customHeight="1">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>1. Customized — Sim behavior Arena changed</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Billing and workspaces</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Credits debit matches ledger after one Agent turn</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>1. Note remaining credits / known balance.
 2. Run one Agent turn.
 3. Compare Usage dashboard debit to the ledger entry (credits-per-dollar).</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>Dashboard debit matches the ledger entry for that turn. No unexplained extra debit.</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37" ht="90" customHeight="1">
-      <c r="A37" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="90" customHeight="1">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>1. Customized — Sim behavior Arena changed</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>Billing and workspaces</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Cost block amount shows once (no double charge)</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>1. Run a workflow with an Agent model cost and an explicit Cost block amount.
 2. Inspect the run’s usage rows.</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>Explicit Cost block amount appears once. No double charge vs the Agent model cost.</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr"/>
-      <c r="I37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38" ht="90" customHeight="1">
-      <c r="A38" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44" ht="90" customHeight="1">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>1. Customized — Sim behavior Arena changed</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Billing and workspaces</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Usage-log multiplier: one scaled ledger row</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>1. Run a metered tool that uses the usage-log multiplier.
 2. Inspect ledger rows for that run.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>Exactly one scaled ledger row is written — not a raw row plus a scaled duplicate.</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39" ht="90" customHeight="1">
-      <c r="A39" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="90" customHeight="1">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>1. Customized — Sim behavior Arena changed</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>Billing and workspaces</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Signup personal workspace; /workspace fallback</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>1. Sign up a new user (or use a fresh account path).
 2. Visit /workspace with no id.</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>Signup creates a personal workspace. /workspace fallback lands on a valid workspace.</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40" ht="90" customHeight="1">
-      <c r="A40" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46" ht="90" customHeight="1">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>1. Customized — Sim behavior Arena changed</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Billing and workspaces</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Daily credit refresh off unless explicitly enabled</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>1. Confirm env does not enable daily refresh (default Arena).
 2. Observe that daily refresh does not run.
 3. If a test env enables it, confirm it then runs.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>Daily refresh stays off by default. It only runs when the environment explicitly enables it.</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41" ht="90" customHeight="1">
-      <c r="A41" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47" ht="90" customHeight="1">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>1. Customized — Sim behavior Arena changed</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Billing and workspaces</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>X-Sim-Email bills the named user’s org once</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the deploy-modal API sample and confirm X-Sim-Email is present.
+2. Execute the workflow API with X-Sim-Email set to a Sim user in another organization.
+3. Compare Usage for the billed org and the workflow’s owning workspace.
+4. Repeat with a missing header, a malformed email, and an email that matches no user.</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>The run bills the named user’s org once. The owning workspace does not also debit it. The billed org’s Usage shows a By Agent row (workflow, owning org · workspace, Run by) and remaining credits drop by that run. A missing header or malformed email is 400. An unknown email is 400 with BILLING_EMAIL_NOT_FOUND.</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48" ht="90" customHeight="1">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>1. Customized — Sim behavior Arena changed</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Workflow engine</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Response inside loop continues; outside ends</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>1. Build a loop with a Response inside; run.
 2. Build a workflow with a Response outside any loop; run.</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>Response inside a loop continues the loop. Response outside a loop ends the workflow.</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42" ht="90" customHeight="1">
-      <c r="A42" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49" ht="90" customHeight="1">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>1. Customized — Sim behavior Arena changed</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>Workflow engine</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Empty forEach still runs the block after the loop</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>1. Build a forEach over an empty collection with a successor block after the loop.
 2. Run the workflow.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>Loop body is skipped. The block after the loop still executes.</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43" ht="90" customHeight="1">
-      <c r="A43" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50" ht="90" customHeight="1">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>1. Customized — Sim behavior Arena changed</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>Workflow engine</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Nested loops and nested subflows save and run</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>1. Create nested loops / nested subflows (Arena allows; upstream rejects).
 2. Save and run.</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>Nested structures save and run successfully.</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr"/>
-      <c r="I43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44" ht="90" customHeight="1">
-      <c r="A44" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51" ht="90" customHeight="1">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>1. Customized — Sim behavior Arena changed</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>Workflow engine</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Agent model picker: OpenRouter free-only; Azure Anthropic + image models</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>1. Open Agent model picker.
 2. Inspect OpenRouter list pricing.
 3. Confirm Azure Anthropic and Arena-added image models appear where expected.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>OpenRouter list is free-only. Azure Anthropic and Arena image models still appear.</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr"/>
-      <c r="I44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45" ht="90" customHeight="1">
-      <c r="A45" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52" ht="90" customHeight="1">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>1. Customized — Sim behavior Arena changed</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>Workflow engine</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Run logs/console show charts, images, acting user</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>1. Run a workflow that produces chart and image payloads.
 2. Open console and logs for the run.</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>Chart payloads, image payloads, and the acting user are visible in run logs/console.</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr"/>
-      <c r="I45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46" ht="90" customHeight="1">
-      <c r="A46" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53" ht="90" customHeight="1">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>1. Customized — Sim behavior Arena changed</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>Extended integrations</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Slack: search, user-channel lookup, and post</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>1. Run Slack search and user-channel lookup (Arena extras).
-2. Run a normal Slack post.</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Extra ops and stock post each return data / succeed once.</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr"/>
-      <c r="I46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47" ht="90" customHeight="1">
-      <c r="A47" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Slack: Arena Bot and Custom Bot, search, post, and Copilot Connect</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>1. In the Slack block, select Arena Bot (bot token) and Custom Bot (user token).
+2. Run Slack search, user-channel lookup, and a normal post.
+3. Ask Copilot to connect Slack while it is disconnected.</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Both auth methods are selectable. Search, lookup, and post each succeed once. Copilot shows one Connect control (“Connect these, then continue”, button Continue), not a Submit button and not a repeated card.</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54" ht="90" customHeight="1">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>1. Customized — Sim behavior Arena changed</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>Extended integrations</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>HubSpot: campaign op + list contacts</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>1. Run hubspot_get_campaign_metrics (or another campaign op).
-2. Run stock hubspot_list_contacts.</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Both operations return data successfully.</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr"/>
-      <c r="I47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48" ht="90" customHeight="1">
-      <c r="A48" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>HubSpot: Accounts picker, campaign op, list contacts</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>1. On an admin workspace, open the HubSpot block and load the Accounts picker.
+2. Select an account and run a read.
+3. Run hubspot_get_campaign_metrics (or another campaign op) and stock hubspot_list_contacts.</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>The picker loads real portals and the selected account reads successfully. Campaign op and list contacts both return data.</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55" ht="90" customHeight="1">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>1. Customized — Sim behavior Arena changed</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>Extended integrations</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Google Slides: template tables + stock slide action</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>1. Run create-from-template / template tables (Arena path).
 2. Run one stock slide action.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>Template tables path and stock slide action each succeed once.</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49" ht="90" customHeight="1">
-      <c r="A49" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56" ht="90" customHeight="1">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>1. Customized — Sim behavior Arena changed</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Extended integrations</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Zoom: recordings, transcript download, stock meeting</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Fetch account recordings and download a transcript.
 2. Run one stock meeting action.</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>Recordings/transcript path and stock meeting action succeed.</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr"/>
-      <c r="I49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50" ht="90" customHeight="1">
-      <c r="A50" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57" ht="90" customHeight="1">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>1. Customized — Sim behavior Arena changed</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>Extended integrations</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Shopify list customers (success) + list products</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. Run shopify_list_customers; assert downstream can read success.
 2. Run stock shopify_list_products.
 3. Optionally list/get another resource that previously mapped outputs.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>list_customers succeeds and success remains available downstream. list_products succeeds. Output mapping intact.</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr"/>
-      <c r="I50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51" ht="90" customHeight="1">
-      <c r="A51" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>1. Customized — Sim behavior Arena changed</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Extended integrations</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>Gmail: advanced search, read thread, send/read</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>1. Run advanced search and read thread.
-2. Send or read a message.</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>Advanced search/thread and send/read each succeed once.</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr"/>
-      <c r="I51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52" ht="90" customHeight="1">
-      <c r="A52" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>1. Customized — Sim behavior Arena changed</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Extended integrations</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>Google Drive: upload, AI query helpers, stock file read</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>1. Upload a file and run an AI query helper.
-2. Run a stock file read / search.</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>Upload, AI query helpers, and stock file read/search succeed.</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr"/>
-      <c r="I52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53" ht="90" customHeight="1">
-      <c r="A53" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>1. Customized — Sim behavior Arena changed</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Extended integrations</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>Google Ads search: results consumed as array</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>1. Run Google Ads search (GAQL).
-2. Wire a downstream block to results (e.g. forEach or Function).</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>Downstream consumes results as an array (not a bare object / undefined).</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr"/>
-      <c r="I53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54" ht="90" customHeight="1">
-      <c r="A54" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>1. Customized — Sim behavior Arena changed</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Extended integrations</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Image Generator: variations, refs, pick prior image</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>1. Prompt for three variations from one prompt.
-2. Use a reference image.
-3. Pick a previously generated image from the conversation.</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>Multiple variations generate. Reference images work. Prior conversation images can be picked.</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55" ht="90" customHeight="1">
-      <c r="A55" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>1. Customized — Sim behavior Arena changed</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Files</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Generated images/docs open from file serve route</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>1. Generate an image and a compiled document.
-2. Open each via the file serve route.</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>Both open successfully from the file serve route.</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr"/>
-      <c r="I55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56" ht="90" customHeight="1">
-      <c r="A56" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>1. Customized — Sim behavior Arena changed</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Files</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>Org logo upload and display</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>1. Upload an org logo.
-2. Confirm it displays in the shell/branding surfaces.</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>Logo uploads and displays correctly.</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr"/>
-      <c r="I56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57" ht="90" customHeight="1">
-      <c r="A57" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>1. Customized — Sim behavior Arena changed</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Files</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>Editor file upload can pick chat images</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>1. Generate or attach an image in chat.
-2. From the editor file upload, pick an image already in the chat.</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>Editor can select images already present in the chat.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
@@ -2654,1096 +2664,1483 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
+          <t>1. Customized — Sim behavior Arena changed</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Extended integrations</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Gmail: advanced search, read thread, send/read</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>1. Run advanced search and read thread.
+2. Send or read a message.</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Advanced search/thread and send/read each succeed once.</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59" ht="90" customHeight="1">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>1. Customized — Sim behavior Arena changed</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Extended integrations</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Google Drive: upload, AI query helpers, stock file read</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>1. Upload a file and run an AI query helper.
+2. Run a stock file read / search.</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Upload, AI query helpers, and stock file read/search succeed.</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60" ht="90" customHeight="1">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>1. Customized — Sim behavior Arena changed</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Extended integrations</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Google Ads v26 search: results consumed as array</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>1. Run Google Ads search (GAQL) and confirm the request uses API v26.
+2. Wire a downstream block to results (e.g. forEach or Function).</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Search succeeds on v26. Downstream consumes results as an array (not a bare object / undefined).</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61" ht="90" customHeight="1">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>1. Customized — Sim behavior Arena changed</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Extended integrations</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Image Generator: distinct variations, refs, edit</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>1. Prompt “Create 3 distinct variations of …” .
+2. Use a reference image and pick a previously generated image.
+3. Edit that image.</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Three separate images return, not one combined frame. Reference and prior images work. The edit returns an image preview, not an empty or octet-stream file.</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62" ht="90" customHeight="1">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>1. Customized — Sim behavior Arena changed</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Generated images/docs open from file serve route</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>1. Generate an image and a compiled document.
+2. Open each via the file serve route.
+3. Reuse a chat image in a later run and open that file.</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Both open from the file serve route. The reused image is copied onto the run and opens. The path is not a broken or context-query URL.</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63" ht="90" customHeight="1">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>1. Customized — Sim behavior Arena changed</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Org logo upload and display</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>1. Upload an org logo.
+2. Confirm it displays in the shell/branding surfaces.</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Logo uploads and displays correctly.</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64" ht="90" customHeight="1">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>1. Customized — Sim behavior Arena changed</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Editor file upload can pick chat images</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>1. Generate or attach an image in chat.
+2. From the editor file upload, pick an image already in the chat.</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Editor can select images already present in the chat.</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65" ht="90" customHeight="1">
+      <c r="A65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>Local copilot runtime</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Tool calls, patches, audit history persist across reload</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>1. On Local, run a turn that performs tool calls / patches.
 2. Reload the page.
 3. Inspect tool calls, patches, and audit history.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>Tool calls, patches, and audit history persist across reload.</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr"/>
-      <c r="I58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59" ht="90" customHeight="1">
-      <c r="A59" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr"/>
+      <c r="I65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66" ht="90" customHeight="1">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>Local copilot runtime</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>User access and user memory apply to the next turn</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. Configure user access / user memory for Local.
 2. Send a follow-up turn that should use that memory/access.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>Next turn respects user access and user memory.</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr"/>
-      <c r="I59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60" ht="90" customHeight="1">
-      <c r="A60" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67" ht="90" customHeight="1">
+      <c r="A67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>Arena task block</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Create task / with fields / sub-task / with fields</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>1. In the Arena block, run create task.
 2. Create task with fields.
 3. Create sub-task and sub-task with fields.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>All four create operations succeed and return task data.</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61" ht="90" customHeight="1">
-      <c r="A61" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68" ht="90" customHeight="1">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>Arena task block</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Add comment / add comment by task number</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. Add a comment on a task.
 2. Add a comment by task number.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>Both comment operations succeed.</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr"/>
-      <c r="I61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62" ht="90" customHeight="1">
-      <c r="A62" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69" ht="90" customHeight="1">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>Arena task block</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Fetch searched tasks / search task / simple search</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. Run fetch searched tasks.
 2. Run search task.
 3. Run simple search.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>Each search/fetch operation returns matching task data.</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr"/>
-      <c r="I62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63" ht="90" customHeight="1">
-      <c r="A63" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70" ht="90" customHeight="1">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>Arena task block</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Save summary / get meetings / get token</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Run save summary.
 2. Run get meetings.
 3. Run get token.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>Each operation succeeds and returns expected payload.</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr"/>
-      <c r="I63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64" ht="90" customHeight="1">
-      <c r="A64" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71" ht="90" customHeight="1">
+      <c r="A71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>Arena task block</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Get my tasks / get my overdue tasks</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>1. Run get my tasks.
-2. Run get my overdue tasks.</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>Both list operations return the user’s tasks / overdue tasks.</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr"/>
-      <c r="I64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65" ht="90" customHeight="1">
-      <c r="A65" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>1. Run get my tasks and get my overdue tasks from the builder.
+2. Start the same workflow from a schedule or a webhook and run both operations again.
+3. If Arena auth fails, confirm the block returns an error.</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Both operations return the user’s tasks from a manual run and from a schedule or webhook run. A failure is an error, not an empty task list.</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72" ht="90" customHeight="1">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>Arena task block</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Client and project selectors load Arena data</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. Open the Arena block panel.
 2. Open client and project selectors.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>Selectors load real Arena client/project data (not empty stubs / errors).</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr"/>
-      <c r="I65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66" ht="90" customHeight="1">
-      <c r="A66" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73" ht="90" customHeight="1">
+      <c r="A73" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>Arena Development and generated apps</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Arena Development: edit an Arena app</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>1. Add Arena Development block.
 2. Edit an existing Arena app.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>Edit succeeds and persists for the Arena app.</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr"/>
-      <c r="I66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67" ht="90" customHeight="1">
-      <c r="A67" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74" ht="90" customHeight="1">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>Arena Development and generated apps</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Development: generate, edit, deploy to Vercel</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>1. Generate an app with the Development block.
 2. Edit it.
 3. Deploy to Vercel.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>Generate, edit, and Vercel deploy each succeed.</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr"/>
-      <c r="I67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68" ht="90" customHeight="1">
-      <c r="A68" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75" ht="90" customHeight="1">
+      <c r="A75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>Arena Development and generated apps</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Skill share across workspace/org</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>1. Publish a skill into the catalog.
 2. Use/copy it in another workspace or org.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>Published skill is usable from the other workspace/org.</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr"/>
-      <c r="I68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69" ht="90" customHeight="1">
-      <c r="A69" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76" ht="90" customHeight="1">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>Exclusive blocks</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Bing Ads, Facebook Ads, Google Ads V1</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>1. Confirm each block appears in the block menu.
 2. Run one NL or GAQL/query op per product.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>Blocks appear. One operation per product returns data.</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr"/>
-      <c r="I69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70" ht="90" customHeight="1">
-      <c r="A70" s="2" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77" ht="90" customHeight="1">
+      <c r="A77" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
         <is>
           <t>Exclusive blocks</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Figma file read or design action</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>1. Confirm Figma is in the block menu.
 2. Run a file read or design action.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>Block visible; operation returns data.</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr"/>
-      <c r="I70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71" ht="90" customHeight="1">
-      <c r="A71" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78" ht="90" customHeight="1">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>Exclusive blocks</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Image Fusion</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>1. Confirm Image Fusion is in the menu.
 2. Fuse two or more images into one output.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>Fused image is produced from multiple inputs.</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr"/>
-      <c r="I71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72" ht="90" customHeight="1">
-      <c r="A72" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79" ht="90" customHeight="1">
+      <c r="A79" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>Exclusive blocks</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>P2 Docs</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>1. Confirm P2 Docs is in the menu.
 2. Run template schema, icons, or team data once.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>Block visible; chosen operation returns data.</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr"/>
-      <c r="I72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73" ht="90" customHeight="1">
-      <c r="A73" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80" ht="90" customHeight="1">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>Exclusive blocks</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Semrush and SpyFu</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>1. Confirm both appear in the menu.
 2. Run one SEO query on each.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>Each returns SEO query data once.</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr"/>
-      <c r="I73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74" ht="90" customHeight="1">
-      <c r="A74" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81" ht="90" customHeight="1">
+      <c r="A81" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
         <is>
           <t>Exclusive blocks</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>LinkedIn via Unipile</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>1. Confirm Unipile/LinkedIn block is available.
 2. Read company or profile.
 3. Exercise hosted auth / reconnect if needed.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>Read succeeds. Hosted auth / reconnect works when required.</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr"/>
-      <c r="I74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75" ht="90" customHeight="1">
-      <c r="A75" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82" ht="90" customHeight="1">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>Exclusive blocks</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Chart Generator</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>1. Confirm Chart Generator is in the menu.
 2. Produce ECharts JSON and render in chat.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>Chat renderer draws the chart from the JSON output.</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr"/>
-      <c r="I75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76" ht="90" customHeight="1">
-      <c r="A76" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83" ht="90" customHeight="1">
+      <c r="A83" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>Exclusive blocks</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Skyvern create or get run</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>1. If credentials exist, create or get a Skyvern run.
 2. Otherwise mark N/A with ticket/env note.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>Successful create/get, or explicit N/A with ticket reference when no credential.</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr"/>
-      <c r="I76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77" ht="90" customHeight="1">
-      <c r="A77" s="2" t="n">
-        <v>76</v>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84" ht="90" customHeight="1">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>Exclusive blocks</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Airweave successful run</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>1. Confirm Airweave visibility for this product build.
 2. Run once, or N/A with ticket if product does not ship it.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>One successful run, or N/A with ticket reference.</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr"/>
-      <c r="I77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78" ht="90" customHeight="1">
-      <c r="A78" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85" ht="90" customHeight="1">
+      <c r="A85" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
         <is>
           <t>Deployed-chat extras</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Departments, assistant assets, banners, prompt feedback, golden queries</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>1. Configure/verify departments, assistant assets, banner messages.
 2. Exercise prompt feedback and workflow golden queries on deployed chat.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>All Arena-only extras render and function; golden queries work with the extras pack.</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr"/>
-      <c r="I78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79" ht="90" customHeight="1">
-      <c r="A79" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86" ht="90" customHeight="1">
+      <c r="A86" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
         <is>
           <t>Deployed-chat extras</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Thread list in left nav; theme sync with Arena shell</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>1. Open deployed chat left nav thread list.
 2. Compare theme with the Arena shell.</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>Thread list works. Theme syncs with the Arena shell.</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr"/>
-      <c r="I79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80" ht="90" customHeight="1">
-      <c r="A80" s="2" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87" ht="90" customHeight="1">
+      <c r="A87" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
         <is>
           <t>Admin, identity, and ops</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Arena SSO login, resume, legacy cookie clear</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>1. Log in via Arena SSO.
 2. Resume a session into Sim.
 3. On a user with an old host-only session cookie, sign out/clear and confirm legacy cookies expire.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>Login and resume work. Legacy session cookies are cleared (including __Secure- / Domain variants).</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr"/>
-      <c r="I80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81" ht="90" customHeight="1">
-      <c r="A81" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88" ht="90" customHeight="1">
+      <c r="A88" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>Admin, identity, and ops</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Custom OAuth apps at org level</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>1. Configure a custom OAuth app at org level with allowed workspaces.
-2. Connect from an allowed workspace; deny/block from a disallowed one if applicable.</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>Allowed workspaces can use the app. Restrictions respect org configuration.</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr"/>
-      <c r="I81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82" ht="90" customHeight="1">
-      <c r="A82" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>1. Open Settings → Custom OAuth Apps.
+2. Configure an org-level app with allowed workspaces.
+3. Connect from an allowed workspace; try a disallowed one if applicable.</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>The section shows the apps form, not a blank page. Allowed workspaces can use the app. Restrictions respect org configuration.</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89" ht="90" customHeight="1">
+      <c r="A89" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
         <is>
           <t>Admin, identity, and ops</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Agent access requests</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>1. As a platform-admin email, open Settings → Agent access requests.
+2. Approve one request.
+3. As the requester, open the agents list.</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>The settings page opens. After approval the requester sees that agent enabled.</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90" ht="90" customHeight="1">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>2. Exclusive — Arena-only</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Agents list and video builder</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Agents list allow-list and undeploy</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>1. With an email on an agent allow-list, open global, shared-with-me, and my-agents.
+2. Repeat with an email outside the list.
+3. Undeploy the chat agent and reload each list. Also confirm an inactive chat is absent.</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>An allowed email sees the agent enabled. An outside email sees it disabled or absent for that tab. Undeploy removes it from all three lists. An inactive chat is not listed.</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91" ht="90" customHeight="1">
+      <c r="A91" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>2. Exclusive — Arena-only</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Agents list and video builder</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Video builder emailId and Fal usage</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>1. From the Arena agents list, open the video builder app while signed in.
+2. Open that same agent detail with emailId omitted, and open a different agent with emailId omitted.
+3. Make a Fal call from the video app and open the Arena user’s usage ledger.</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>The video builder URL has the logged-in email as emailId, replacing any saved email. Omitting emailId still returns the video builder app and rejects every other agent. The Fal call appears on that user’s usage ledger.</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92" ht="90" customHeight="1">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>2. Exclusive — Arena-only</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Admin, identity, and ops</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Help and support issue filed and stored</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>1. File a help/support issue via the Arena help path.
 2. Confirm it is stored (DB / admin view).</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>Issue is accepted and stored.</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr"/>
-      <c r="I82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83" ht="90" customHeight="1">
-      <c r="A83" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93" ht="90" customHeight="1">
+      <c r="A93" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
         <is>
           <t>Admin, identity, and ops</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>App banner route and workspace embed page</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>1. Open the app banner route inside the host frame.
 2. Open the workspace embed page inside the host frame.</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>Both render correctly inside the host frame.</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr"/>
-      <c r="I83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84" ht="90" customHeight="1">
-      <c r="A84" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="H93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94" ht="90" customHeight="1">
+      <c r="A94" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
         <is>
           <t>Admin, identity, and ops</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Default workflows import and deploy for new user</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>1. Provision or use a new user.
 2. Confirm default workflows import and can deploy.</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>Default workflows import and deploy for the new user.</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr"/>
-      <c r="I84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85" ht="90" customHeight="1">
-      <c r="A85" s="2" t="n">
-        <v>84</v>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="H94" s="2" t="inlineStr"/>
+      <c r="I94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95" ht="90" customHeight="1">
+      <c r="A95" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
         <is>
           <t>Admin, identity, and ops</t>
         </is>
       </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>User knowledge base populate attaches to user</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>1. Trigger user knowledge base populate.
 2. Confirm attachment to the user.</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>KB populate attaches to the user and is usable afterward.</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr"/>
-      <c r="I85" s="2" t="inlineStr"/>
-    </row>
-    <row r="86" ht="90" customHeight="1">
-      <c r="A86" s="2" t="n">
-        <v>85</v>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96" ht="90" customHeight="1">
+      <c r="A96" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
         <is>
           <t>Admin, identity, and ops</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Arena general settings (timezone and events)</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>1. Open /workspace/arena-general-settings (no workspace id required).
 2. Save timezone and events.
@@ -3751,1300 +4148,923 @@
 4. Spot-check workspace /settings/general still works.</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>Page opens without a workspace id. Timezone/events save and apply to chat and copilot. Workspace general settings unchanged.</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr"/>
-      <c r="I86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87" ht="90" customHeight="1">
-      <c r="A87" s="2" t="n">
-        <v>86</v>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr"/>
+      <c r="I96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97" ht="90" customHeight="1">
+      <c r="A97" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
         <is>
           <t>Billing package (Arena-only)</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Starter provisioned for a new client org</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>1. Provision a new client org through the Arena path.
 2. Inspect subscription / usage limit.</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>Starter is provisioned with expected usage limit / metadata.</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr"/>
-      <c r="I87" s="2" t="inlineStr"/>
-    </row>
-    <row r="88" ht="90" customHeight="1">
-      <c r="A88" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="H97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98" ht="90" customHeight="1">
+      <c r="A98" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>Billing package (Arena-only)</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Pro and Max checkout (team_1950 / team_6500)</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>1. As org admin, open upgrade.
 2. Start Pro (team_1950) and/or Max (team_6500) checkout.
 3. Confirm Starter Stripe id is not used for paid checkout.</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>Catalog shows Pro/Max flat org pricing. Checkout ignores Starter Stripe id. Paid checkout can proceed from active Starter.</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr"/>
-      <c r="I88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89" ht="90" customHeight="1">
-      <c r="A89" s="2" t="n">
-        <v>88</v>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="H98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99" ht="90" customHeight="1">
+      <c r="A99" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
         <is>
           <t>Billing package (Arena-only)</t>
         </is>
       </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Org-admin upgrade comparison overlay</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>1. As org admin, open the upgrade comparison overlay.
 2. Review Starter / Max / Enterprise columns (Pro hidden from comparison table).</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>Overlay shows Arena comparison with flat org pricing copy. Pro is not a comparison column.</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr"/>
-      <c r="I89" s="2" t="inlineStr"/>
-    </row>
-    <row r="90" ht="90" customHeight="1">
-      <c r="A90" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="H99" s="2" t="inlineStr"/>
+      <c r="I99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100" ht="90" customHeight="1">
+      <c r="A100" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
         <is>
           <t>Billing package (Arena-only)</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Seat reconcile does not fight flat org pricing</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>1. With an Arena flat org plan, adjust seats / membership.
 2. Observe seat reconcile / pricing behaviour.</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>Seat reconcile does not multiply or fight flat org pricing.</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr"/>
-      <c r="I90" s="2" t="inlineStr"/>
-    </row>
-    <row r="91" ht="90" customHeight="1">
-      <c r="A91" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="H100" s="2" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101" ht="90" customHeight="1">
+      <c r="A101" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
         <is>
           <t>Billing package (Arena-only)</t>
         </is>
       </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Usage limit blocks when exhausted; allows when not</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>1. With credits remaining, run a billable action.
 2. Exhaust credits (or use a test org at limit) and retry.</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t>Run allowed under limit. Run blocked when credits are exhausted.</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr"/>
-      <c r="I91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92" ht="90" customHeight="1">
-      <c r="A92" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="H101" s="2" t="inlineStr"/>
+      <c r="I101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102" ht="90" customHeight="1">
+      <c r="A102" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
         <is>
           <t>Billing package (Arena-only)</t>
         </is>
       </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Paying supersedes Starter; client-org Starter still provisions</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>1. Confirm a new client org still gets Starter.
 2. Complete paid checkout and verify Starter is superseded.</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>Starter provisioning still runs for client orgs. Paying supersedes Starter.</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr"/>
-      <c r="I92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93" ht="90" customHeight="1">
-      <c r="A93" s="2" t="n">
-        <v>92</v>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="H102" s="2" t="inlineStr"/>
+      <c r="I102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103" ht="90" customHeight="1">
+      <c r="A103" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>3. Other Sim features — stock regression</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
         <is>
           <t>Builder core</t>
         </is>
       </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Create, rename, duplicate, delete; undo/redo</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>1. Create a workflow; rename; duplicate; delete.
 2. Exercise undo and redo on canvas edits.</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>CRUD works. Undo/redo restores prior canvas state.</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr"/>
-      <c r="I93" s="2" t="inlineStr"/>
-    </row>
-    <row r="94" ht="90" customHeight="1">
-      <c r="A94" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="H103" s="2" t="inlineStr"/>
+      <c r="I103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104" ht="90" customHeight="1">
+      <c r="A104" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>3. Other Sim features — stock regression</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
         <is>
           <t>Builder core</t>
         </is>
       </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Drag blocks, connect edges, editor panel, variables</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>1. Drag blocks onto the canvas and connect edges.
 2. Open the editor panel.
 3. Use a &lt;Block.output&gt; variable reference.</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t>Blocks connect. Panel opens. Variables resolve.</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr"/>
-      <c r="I94" s="2" t="inlineStr"/>
-    </row>
-    <row r="95" ht="90" customHeight="1">
-      <c r="A95" s="2" t="n">
-        <v>94</v>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="H104" s="2" t="inlineStr"/>
+      <c r="I104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105" ht="90" customHeight="1">
+      <c r="A105" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>3. Other Sim features — stock regression</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
         <is>
           <t>Builder core</t>
         </is>
       </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Manual run, stop, console; logs page</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>1. Manual run a workflow; stop mid-run if possible.
 2. Read the console.
 3. Open the Logs page for the same run.</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>Run/stop/console work. Logs page shows the same run.</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr"/>
-      <c r="I95" s="2" t="inlineStr"/>
-    </row>
-    <row r="96" ht="90" customHeight="1">
-      <c r="A96" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="H105" s="2" t="inlineStr"/>
+      <c r="I105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106" ht="90" customHeight="1">
+      <c r="A106" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>3. Other Sim features — stock regression</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
         <is>
           <t>Builder core</t>
         </is>
       </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Save/reload; realtime second user</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>1. Save and reload the workflow.
 2. Have a second user open the same workflow and make an edit.</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>State persists after reload. Second user sees realtime updates.</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr"/>
-      <c r="I96" s="2" t="inlineStr"/>
-    </row>
-    <row r="97" ht="90" customHeight="1">
-      <c r="A97" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="H106" s="2" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107" ht="90" customHeight="1">
+      <c r="A107" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>3. Other Sim features — stock regression</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
         <is>
           <t>Builder core</t>
         </is>
       </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Deploy; API trigger and chat trigger</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>1. Deploy the workflow.
 2. Fire an API trigger and a chat trigger.</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>Each trigger starts a run successfully.</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr"/>
-      <c r="I97" s="2" t="inlineStr"/>
-    </row>
-    <row r="98" ht="90" customHeight="1">
-      <c r="A98" s="2" t="n">
-        <v>97</v>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="H107" s="2" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108" ht="90" customHeight="1">
+      <c r="A108" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>3. Other Sim features — stock regression</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
         <is>
           <t>Builder core</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Schedule trigger and webhook trigger</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>1. Configure a schedule; wait for one fire (or advance in test env).
 2. Send one signed webhook request.</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>Schedule fires once. Webhook accepts the signed request and starts a run.</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr"/>
-      <c r="I98" s="2" t="inlineStr"/>
-    </row>
-    <row r="99" ht="90" customHeight="1">
-      <c r="A99" s="2" t="n">
-        <v>98</v>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr"/>
+      <c r="I108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109" ht="90" customHeight="1">
+      <c r="A109" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>3. Other Sim features — stock regression</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
         <is>
           <t>Builder core</t>
         </is>
       </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Response body; Condition and Router branches</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>1. Configure a Response block body and run.
 2. Configure Condition and Router; take each branch once.</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>Response returns configured body. Condition and Router take the correct branch.</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr"/>
-      <c r="I99" s="2" t="inlineStr"/>
-    </row>
-    <row r="100" ht="90" customHeight="1">
-      <c r="A100" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="H109" s="2" t="inlineStr"/>
+      <c r="I109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110" ht="90" customHeight="1">
+      <c r="A110" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>3. Other Sim features — stock regression</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
         <is>
           <t>Builder core</t>
         </is>
       </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Loop and parallel small inner graph</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>1. Run a small loop inner graph.
 2. Run a small parallel inner graph.
 3. (Nested Arena case already covered in section 1.)</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>Loop and parallel each run the inner graph correctly.</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr"/>
-      <c r="I100" s="2" t="inlineStr"/>
-    </row>
-    <row r="101" ht="90" customHeight="1">
-      <c r="A101" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="H110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111" ht="90" customHeight="1">
+      <c r="A111" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>3. Other Sim features — stock regression</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
         <is>
           <t>Workspace surfaces</t>
         </is>
       </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Home, workflow list, sidebar navigation</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>1. Open home, workflow list, and navigate the sidebar.</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t>All surfaces load and navigate without errors.</t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr"/>
-      <c r="I101" s="2" t="inlineStr"/>
-    </row>
-    <row r="102" ht="90" customHeight="1">
-      <c r="A102" s="2" t="n">
-        <v>101</v>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="H111" s="2" t="inlineStr"/>
+      <c r="I111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112" ht="90" customHeight="1">
+      <c r="A112" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>3. Other Sim features — stock regression</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
         <is>
           <t>Workspace surfaces</t>
         </is>
       </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Knowledge: create base, upload, retrieve from Agent</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>1. Create a knowledge base; upload a document.
-2. Retrieve it from an Agent block.</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>Upload succeeds. Agent retrieval returns the document content/citations.</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr"/>
-      <c r="I102" s="2" t="inlineStr"/>
-    </row>
-    <row r="103" ht="90" customHeight="1">
-      <c r="A103" s="2" t="n">
-        <v>102</v>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
+2. Retrieve it from an Agent block.
+3. Run a search that hits and a search that matches nothing.</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Upload succeeds. Agent retrieval returns the document content/citations. A hit includes rank. An empty search returns an empty result the Agent can consume, with no crash on a missing rank.</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr"/>
+      <c r="I112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113" ht="90" customHeight="1">
+      <c r="A113" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>3. Other Sim features — stock regression</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
         <is>
           <t>Workspace surfaces</t>
         </is>
       </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Tables: create, add row, filter</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>1. Create a table; add a row; apply a filter.</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t>Row appears and filter returns the expected subset.</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr"/>
-      <c r="I103" s="2" t="inlineStr"/>
-    </row>
-    <row r="104" ht="90" customHeight="1">
-      <c r="A104" s="2" t="n">
-        <v>103</v>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="H113" s="2" t="inlineStr"/>
+      <c r="I113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114" ht="90" customHeight="1">
+      <c r="A114" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>3. Other Sim features — stock regression</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr">
         <is>
           <t>Workspace surfaces</t>
         </is>
       </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Files: upload, preview PDF/image, delete</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>1. Upload a PDF and an image.
 2. Preview each; delete one.</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr">
         <is>
           <t>Upload/preview/delete succeed for PDF and image.</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr"/>
-      <c r="I104" s="2" t="inlineStr"/>
-    </row>
-    <row r="105" ht="90" customHeight="1">
-      <c r="A105" s="2" t="n">
-        <v>104</v>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="H114" s="2" t="inlineStr"/>
+      <c r="I114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115" ht="90" customHeight="1">
+      <c r="A115" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>3. Other Sim features — stock regression</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
         <is>
           <t>Workspace surfaces</t>
         </is>
       </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Skills: create and attach to agent</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>1. Create a skill.
 2. Attach it to an agent and run once.</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr">
         <is>
           <t>Skill attaches and is used by the agent run.</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr"/>
-      <c r="I105" s="2" t="inlineStr"/>
-    </row>
-    <row r="106" ht="90" customHeight="1">
-      <c r="A106" s="2" t="n">
-        <v>105</v>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="H115" s="2" t="inlineStr"/>
+      <c r="I115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116" ht="90" customHeight="1">
+      <c r="A116" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>3. Other Sim features — stock regression</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
         <is>
           <t>Workspace surfaces</t>
         </is>
       </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Logs, tests, dashboards, changelog pages load</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>1. Open logs, tests, dashboards, and changelog pages.</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr">
         <is>
           <t>Each page loads without error.</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr"/>
-      <c r="I106" s="2" t="inlineStr"/>
-    </row>
-    <row r="107" ht="90" customHeight="1">
-      <c r="A107" s="2" t="n">
-        <v>106</v>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="H116" s="2" t="inlineStr"/>
+      <c r="I116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117" ht="90" customHeight="1">
+      <c r="A117" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>3. Other Sim features — stock regression</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
+      <c r="C117" s="2" t="inlineStr">
         <is>
           <t>Workspace surfaces</t>
         </is>
       </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Integrations catalog and connected credential</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>1. Open the integrations catalog.
 2. Open a connected credential detail.</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr">
         <is>
           <t>Catalog and credential detail both open.</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr"/>
-      <c r="I107" s="2" t="inlineStr"/>
-    </row>
-    <row r="108" ht="90" customHeight="1">
-      <c r="A108" s="2" t="n">
-        <v>107</v>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="H117" s="2" t="inlineStr"/>
+      <c r="I117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118" ht="90" customHeight="1">
+      <c r="A118" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>3. Other Sim features — stock regression</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
+      <c r="C118" s="2" t="inlineStr">
         <is>
           <t>Workspace surfaces</t>
         </is>
       </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Recently deleted: restore one workflow</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>1. Delete a workflow.
 2. Restore it from Recently deleted.</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr">
         <is>
           <t>Workflow restores and opens.</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr"/>
-      <c r="I108" s="2" t="inlineStr"/>
-    </row>
-    <row r="109" ht="90" customHeight="1">
-      <c r="A109" s="2" t="n">
-        <v>108</v>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="H118" s="2" t="inlineStr"/>
+      <c r="I118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119" ht="90" customHeight="1">
+      <c r="A119" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>3. Other Sim features — stock regression</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
+      <c r="C119" s="2" t="inlineStr">
         <is>
           <t>Settings</t>
         </is>
       </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Account, teammates, org members, secrets, credential groups</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>1. Open each settings page and perform a trivial save/view.</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr">
         <is>
           <t>Each page loads; trivial actions succeed.</t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr"/>
-      <c r="I109" s="2" t="inlineStr"/>
-    </row>
-    <row r="110" ht="90" customHeight="1">
-      <c r="A110" s="2" t="n">
-        <v>109</v>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="H119" s="2" t="inlineStr"/>
+      <c r="I119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120" ht="90" customHeight="1">
+      <c r="A120" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>3. Other Sim features — stock regression</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
+      <c r="C120" s="2" t="inlineStr">
         <is>
           <t>Settings</t>
         </is>
       </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Arena API keys: create, use on API trigger, revoke</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>1. Create an Arena API key.
 2. Use it on an API trigger.
 3. Revoke it and confirm rejection.</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr">
         <is>
           <t>Create/use succeed. After revoke, the key is rejected.</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr"/>
-      <c r="I110" s="2" t="inlineStr"/>
-    </row>
-    <row r="111" ht="90" customHeight="1">
-      <c r="A111" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>3. Other Sim features — stock regression</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>Settings</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>Custom tools, MCP tools, MCP servers, sandboxes</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>1. Open each settings surface.
-2. Spot-check one create/connect action if credentials allow.</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>Surfaces load; spot-check action succeeds or is N/A with reason.</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="inlineStr"/>
-      <c r="I111" s="2" t="inlineStr"/>
-    </row>
-    <row r="112" ht="90" customHeight="1">
-      <c r="A112" s="2" t="n">
-        <v>111</v>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>3. Other Sim features — stock regression</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>Settings</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>Permission groups and audit logs (enterprise)</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>1. If the org has enterprise, open permission groups and audit logs.
-2. Otherwise mark N/A.</t>
-        </is>
-      </c>
-      <c r="G112" s="2" t="inlineStr">
-        <is>
-          <t>Pages load for enterprise orgs; N/A otherwise.</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr"/>
-      <c r="I112" s="2" t="inlineStr"/>
-    </row>
-    <row r="113" ht="90" customHeight="1">
-      <c r="A113" s="2" t="n">
-        <v>112</v>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>3. Other Sim features — stock regression</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>Settings</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr">
-        <is>
-          <t>Subscription page matches Arena plan</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the subscription page.
-2. Compare to the Arena plan verified in section 2 billing.</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t>Subscription page matches the Arena plan (Starter/Pro/Max).</t>
-        </is>
-      </c>
-      <c r="H113" s="2" t="inlineStr"/>
-      <c r="I113" s="2" t="inlineStr"/>
-    </row>
-    <row r="114" ht="90" customHeight="1">
-      <c r="A114" s="2" t="n">
-        <v>113</v>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>3. Other Sim features — stock regression</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>Agent and model path</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>Agent block calls allowed model and returns text</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>1. Configure an Agent block with one allowed model.
-2. Run and read the text output.</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>Agent returns text from the allowed model.</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr"/>
-      <c r="I114" s="2" t="inlineStr"/>
-    </row>
-    <row r="115" ht="90" customHeight="1">
-      <c r="A115" s="2" t="n">
-        <v>114</v>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>3. Other Sim features — stock regression</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>Agent and model path</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>Tools the agent calls show in the trace</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>1. Run an Agent that calls at least one tool.
-2. Inspect the run trace.</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t>Tool calls appear in the trace.</t>
-        </is>
-      </c>
-      <c r="H115" s="2" t="inlineStr"/>
-      <c r="I115" s="2" t="inlineStr"/>
-    </row>
-    <row r="116" ht="90" customHeight="1">
-      <c r="A116" s="2" t="n">
-        <v>115</v>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>3. Other Sim features — stock regression</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>Agent and model path</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>Memory survives a second run in the same thread</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>1. Run an Agent with memory in a thread.
-2. Run a second turn in the same thread that depends on memory.</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>Second run uses memory from the first.</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr"/>
-      <c r="I116" s="2" t="inlineStr"/>
-    </row>
-    <row r="117" ht="90" customHeight="1">
-      <c r="A117" s="2" t="n">
-        <v>116</v>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>3. Other Sim features — stock regression</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>Representative stock integrations</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E117" s="2" t="inlineStr">
-        <is>
-          <t>Google: Calendar, Sheets, Docs (Gmail/Drive covered in §1)</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>1. If credentials exist, run one read/write each for Calendar, Sheets, Docs.
-2. Skip Gmail/Drive here if already passed in section 1 Extended; note in Notes.</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="inlineStr">
-        <is>
-          <t>Each tested Google service succeeds once, or N/A with credential note. Gmail/Drive may be N/A-if-covered-in-§1.</t>
-        </is>
-      </c>
-      <c r="H117" s="2" t="inlineStr"/>
-      <c r="I117" s="2" t="inlineStr"/>
-    </row>
-    <row r="118" ht="90" customHeight="1">
-      <c r="A118" s="2" t="n">
-        <v>117</v>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>3. Other Sim features — stock regression</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>Representative stock integrations</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
-          <t>Microsoft: Outlook, Teams, OneDrive</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>1. With a test account, run one read or write each.</t>
-        </is>
-      </c>
-      <c r="G118" s="2" t="inlineStr">
-        <is>
-          <t>Each succeeds once, or N/A if no credential.</t>
-        </is>
-      </c>
-      <c r="H118" s="2" t="inlineStr"/>
-      <c r="I118" s="2" t="inlineStr"/>
-    </row>
-    <row r="119" ht="90" customHeight="1">
-      <c r="A119" s="2" t="n">
-        <v>118</v>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>3. Other Sim features — stock regression</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>Representative stock integrations</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="inlineStr">
-        <is>
-          <t>Atlassian: Jira, Confluence</t>
-        </is>
-      </c>
-      <c r="F119" s="2" t="inlineStr">
-        <is>
-          <t>1. Run one Jira and one Confluence happy path.</t>
-        </is>
-      </c>
-      <c r="G119" s="2" t="inlineStr">
-        <is>
-          <t>Each succeeds once, or N/A if no credential.</t>
-        </is>
-      </c>
-      <c r="H119" s="2" t="inlineStr"/>
-      <c r="I119" s="2" t="inlineStr"/>
-    </row>
-    <row r="120" ht="90" customHeight="1">
-      <c r="A120" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>3. Other Sim features — stock regression</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>Representative stock integrations</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E120" s="2" t="inlineStr">
-        <is>
-          <t>Dev: GitHub, Linear (or Jira if Linear unavailable)</t>
-        </is>
-      </c>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>1. Run one GitHub action.
-2. Run one Linear or Jira action.</t>
-        </is>
-      </c>
-      <c r="G120" s="2" t="inlineStr">
-        <is>
-          <t>Each succeeds once, or N/A if no credential.</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr"/>
@@ -5061,7 +5081,7 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Representative stock integrations</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -5071,18 +5091,18 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Comms: Discord and Microsoft Teams (Slack covered in §1)</t>
+          <t>Custom tools, MCP tools, MCP servers, sandboxes</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>1. Run Discord and Teams stock ops.
-2. Mark Slack N/A if already covered by section 1 Extended Slack.</t>
+          <t>1. Open each settings surface.
+2. Spot-check one create/connect action if credentials allow.</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Discord/Teams succeed once, or N/A. Slack noted as covered in §1 when applicable.</t>
+          <t>Surfaces load; spot-check action succeeds or is N/A with reason.</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr"/>
@@ -5099,7 +5119,7 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Representative stock integrations</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -5109,18 +5129,18 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>CRM: Salesforce stock read (HubSpot covered in §1)</t>
+          <t>Permission groups and audit logs (enterprise)</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>1. Run a Salesforce stock read if credentialed.
-2. Mark HubSpot N/A if already covered in section 1.</t>
+          <t>1. If the org has enterprise, open permission groups and audit logs.
+2. Otherwise mark N/A.</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Salesforce succeeds once, or N/A. HubSpot noted as covered in §1 when applicable.</t>
+          <t>Pages load for enterprise orgs; N/A otherwise.</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr"/>
@@ -5137,7 +5157,7 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Representative stock integrations</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -5147,18 +5167,18 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Data: Airtable or Notion; Postgres or built-in table</t>
+          <t>Subscription page matches Arena plan</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>1. Run one Airtable or Notion op.
-2. Run one Postgres or built-in table op.</t>
+          <t>1. Open the subscription page.
+2. Compare to the Arena plan verified in section 2 billing.</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Each chosen path succeeds once, or N/A if no credential.</t>
+          <t>Subscription page matches the Arena plan (Starter/Pro/Max).</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr"/>
@@ -5175,27 +5195,28 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Representative stock integrations</t>
+          <t>Agent and model path</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>AI utilities: Search, Function, API block, Evaluator</t>
+          <t>Agent block calls allowed model and returns text</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>1. Run one happy path each for Search, Function, API block, Evaluator.</t>
+          <t>1. Configure an Agent block with one allowed model.
+2. Run and read the text output.</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>All four succeed once.</t>
+          <t>Agent returns text from the allowed model.</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr"/>
@@ -5212,7 +5233,7 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Auth and tenancy</t>
+          <t>Agent and model path</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -5222,18 +5243,18 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Email sign-in and sign-out; invite and accept</t>
+          <t>Tools the agent calls show in the trace</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>1. Sign in with email; sign out.
-2. Invite a member and accept the invite.</t>
+          <t>1. Run an Agent that calls at least one tool.
+2. Inspect the run trace.</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Sign-in/out work. Invite accept grants membership.</t>
+          <t>Tool calls appear in the trace.</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr"/>
@@ -5250,7 +5271,7 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Auth and tenancy</t>
+          <t>Agent and model path</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -5260,17 +5281,18 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Member cannot open another org’s workspace</t>
+          <t>Memory survives a second run in the same thread</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>1. As a member of org A, attempt to open org B’s workspace URL.</t>
+          <t>1. Run an Agent with memory in a thread.
+2. Run a second turn in the same thread that depends on memory.</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Access is denied; workspace from another org is not opened.</t>
+          <t>Second run uses memory from the first.</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr"/>
@@ -5287,28 +5309,28 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Auth and tenancy</t>
+          <t>Representative stock integrations</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Archived workspace is not selectable</t>
+          <t>Google: Calendar, Sheets, Docs (Gmail/Drive covered in §1)</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>1. Archive a workspace (or use a known archived one).
-2. Try to select it from the workspace picker.</t>
+          <t>1. If credentials exist, run one read/write each for Calendar, Sheets, Docs.
+2. Skip Gmail/Drive here if already passed in section 1 Extended; note in Notes.</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Archived workspace is not selectable.</t>
+          <t>Each tested Google service succeeds once, or N/A with credential note. Gmail/Drive may be N/A-if-covered-in-§1.</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr"/>
@@ -5325,37 +5347,413 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
+          <t>Representative stock integrations</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft: Outlook, Teams, OneDrive</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>1. With a test account, run one read or write each.</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>Each succeeds once, or N/A if no credential.</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr"/>
+      <c r="I128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129" ht="90" customHeight="1">
+      <c r="A129" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>3. Other Sim features — stock regression</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Representative stock integrations</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>Atlassian: Jira, Confluence</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>1. Run one Jira and one Confluence happy path.</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>Each succeeds once, or N/A if no credential.</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr"/>
+      <c r="I129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130" ht="90" customHeight="1">
+      <c r="A130" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>3. Other Sim features — stock regression</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Representative stock integrations</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>Dev: GitHub, Linear (or Jira if Linear unavailable)</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>1. Run one GitHub action.
+2. Run one Linear or Jira action.</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>Each succeeds once, or N/A if no credential.</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr"/>
+      <c r="I130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131" ht="90" customHeight="1">
+      <c r="A131" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>3. Other Sim features — stock regression</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Representative stock integrations</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>Comms: Discord and Microsoft Teams (Slack covered in §1)</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>1. Run Discord and Teams stock ops.
+2. Mark Slack N/A if already covered by section 1 Extended Slack.</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>Discord/Teams succeed once, or N/A. Slack noted as covered in §1 when applicable.</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr"/>
+      <c r="I131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132" ht="90" customHeight="1">
+      <c r="A132" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>3. Other Sim features — stock regression</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Representative stock integrations</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>CRM: Salesforce stock read (HubSpot covered in §1)</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>1. Run a Salesforce stock read if credentialed.
+2. Mark HubSpot N/A if already covered in section 1.</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>Salesforce succeeds once, or N/A. HubSpot noted as covered in §1 when applicable.</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr"/>
+      <c r="I132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133" ht="90" customHeight="1">
+      <c r="A133" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>3. Other Sim features — stock regression</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Representative stock integrations</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>Data: Airtable or Notion; Postgres or built-in table</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>1. Run one Airtable or Notion op.
+2. Run one Postgres or built-in table op.</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>Each chosen path succeeds once, or N/A if no credential.</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr"/>
+      <c r="I133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134" ht="90" customHeight="1">
+      <c r="A134" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>3. Other Sim features — stock regression</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Representative stock integrations</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>AI utilities: Search, Function, API block, Evaluator</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>1. Run one happy path each for Search, Function, API block, Evaluator.</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>All four succeed once.</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr"/>
+      <c r="I134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135" ht="90" customHeight="1">
+      <c r="A135" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>3. Other Sim features — stock regression</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
           <t>Auth and tenancy</t>
         </is>
       </c>
-      <c r="D128" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>Email sign-in and sign-out; invite and accept</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>1. Sign in with email; sign out.
+2. Invite a member and accept the invite.</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>Sign-in/out work. Invite accept grants membership.</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr"/>
+      <c r="I135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136" ht="90" customHeight="1">
+      <c r="A136" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>3. Other Sim features — stock regression</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Auth and tenancy</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>Member cannot open another org’s workspace</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>1. As a member of org A, attempt to open org B’s workspace URL.</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>Access is denied; workspace from another org is not opened.</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr"/>
+      <c r="I136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137" ht="90" customHeight="1">
+      <c r="A137" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>3. Other Sim features — stock regression</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Auth and tenancy</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>Archived workspace is not selectable</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>1. Archive a workspace (or use a known archived one).
+2. Try to select it from the workspace picker.</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>Archived workspace is not selectable.</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr"/>
+      <c r="I137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138" ht="90" customHeight="1">
+      <c r="A138" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>3. Other Sim features — stock regression</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Auth and tenancy</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>API key from another workspace is rejected</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>1. Take an API key from workspace A.
 2. Call a protected API scoped to workspace B.</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr">
         <is>
           <t>Request is rejected (unauthorized / wrong workspace).</t>
         </is>
       </c>
-      <c r="H128" s="2" t="inlineStr"/>
-      <c r="I128" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr"/>
+      <c r="I138" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I128"/>
+  <autoFilter ref="A1:I138"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H128" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid result" error="Choose Pass, Fail, or N/A" type="list">
+    <dataValidation sqref="H2:H138" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid result" error="Choose Pass, Fail, or N/A" type="list">
       <formula1>"Pass,Fail,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5503,14 +5901,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5. P1 customized Slack, HubSpot, Zoom, Slides, Shopify, Gmail, Drive, image variations.</t>
+          <t>5. P1 customized Slack (Arena Bot and Copilot Connect), HubSpot Accounts, Zoom, Slides, Shopify, Gmail, Drive, distinct image variations, and image edit.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6. P2 stock surfaces and a short integration sample (skip services already covered in §1).</t>
+          <t>6. P0 video builder emailId, agents-list undeploy, and X-Sim-Email cross-org billing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>7. P2 stock surfaces and a short integration sample (skip services already covered in §1).</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5929,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kept rows: 127 (P0=70, P1=36, P2=21)</t>
+          <t>Kept rows: 137 (P0=77, P1=39, P2=21)</t>
         </is>
       </c>
     </row>

--- a/docs/upstream/manual-regression-checklist-qa.xlsx
+++ b/docs/upstream/manual-regression-checklist-qa.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Checklist" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Run info" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Dedup log" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run info" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dedup log" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Checklist'!$A$1:$I$138</definedName>
@@ -570,7 +570,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>1. On version-6.1-main: bun run apps/sim/scripts/diff-block-output-contracts.ts dump --out /tmp/output-contracts-before.json
+          <t>1. On version-6.2-main: bun run apps/sim/scripts/diff-block-output-contracts.ts dump --out /tmp/output-contracts-before.json
 2. On the sync branch: bun run apps/sim/scripts/diff-block-output-contracts.ts diff /tmp/output-contracts-before.json
 3. Compare removals/type changes to the sync report.</t>
         </is>

--- a/docs/upstream/manual-regression-checklist-qa.xlsx
+++ b/docs/upstream/manual-regression-checklist-qa.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dedup log" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Checklist'!$A$1:$I$138</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Checklist'!$A$1:$I$139</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dedup log'!$A$1:$C$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I138"/>
+  <dimension ref="A1:I139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1795,18 +1795,20 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Finished Copilot reply does not turn asterisks into bold on scroll</t>
+          <t>Local fork still opens a new chat when the worker has no conversation</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1. Get a Copilot reply that contains ordinary * characters or unfinished markdown.
-2. Wait until the reply has finished, then scroll the thread away and back.</t>
+          <t>1. On Local, finish at least one Copilot reply.
+2. Use Fork in new chat on that reply.
+3. Confirm the new chat opens with a title starting Fork | and the messages up to that reply.
+4. On Cloud, with COPILOT_API_KEY set, fork a finished reply the same way.</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>The finished text stays as it streamed. Scrolling does not turn those characters into bold.</t>
+          <t>Local fork opens the new chat. There is no “Failed to fork chat” toast. Cloud fork still succeeds and keeps the worker conversation.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr"/>
@@ -1828,62 +1830,62 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Finished Copilot reply does not turn asterisks into bold on scroll</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>1. Get a Copilot reply that contains ordinary * characters or unfinished markdown.
+2. Wait until the reply has finished, then scroll the thread away and back.</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>The finished text stays as it streamed. Scrolling does not turn those characters into bold.</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37" ht="90" customHeight="1">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>1. Customized — Sim behavior Arena changed</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Workspace chat and Local/Cloud copilot</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Fetch-and-send sequence is canvas blocks, not Agent tools</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>1. Ask Copilot: today’s calendar, unread Gmail, Slack messages, then a written briefing.
 2. Also ask for a daily time trigger.
 3. Inspect the canvas block types and the Agent tools list.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>The canvas has google_calendar_v2, gmail_v2, and slack as their own blocks in that order. Those integrations are not Agent tools. The daily trigger is a schedule block, not schedule_trigger.</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37" ht="90" customHeight="1">
-      <c r="A37" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>1. Customized — Sim behavior Arena changed</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Workspace chat and Local/Cloud copilot</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Copilot HTML file opens as a complete page</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>1. Ask Copilot to create an HTML page.
-2. Open the saved file.</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>The file opens as a complete page. The chat does not dump a truncated tag soup in place of the file.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
@@ -1905,62 +1907,62 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
+          <t>Copilot HTML file opens as a complete page</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>1. Ask Copilot to create an HTML page.
+2. Open the saved file.</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>The file opens as a complete page. The chat does not dump a truncated tag soup in place of the file.</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39" ht="90" customHeight="1">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>1. Customized — Sim behavior Arena changed</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Workspace chat and Local/Cloud copilot</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
           <t>Local-only users stay on Local without the switch</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as a localOnly allowlisted user.
 2. Open home and workflow Copilot.
 3. Send a message (even if a stale Cloud preference exists).</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>No Local/Cloud switch. Sends stay on Local.</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39" ht="90" customHeight="1">
-      <c r="A39" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>1. Customized — Sim behavior Arena changed</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Workspace chat and Local/Cloud copilot</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Copilot images/files land on Arena ledger</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>1. From Copilot, generate an image and create a file on Local.
-2. Open Usage / ledger.</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Image/file usage appears on the Arena ledger for the Local turns.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr"/>
@@ -1987,18 +1989,18 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Floating workflow chat streams chart/image</t>
+          <t>Copilot images/files land on Arena ledger</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1. Open floating workflow chat.
-2. Run a prompt that produces chart and/or image output.</t>
+          <t>1. From Copilot, generate an image and create a file on Local.
+2. Open Usage / ledger.</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Run streams; chart and image output render in the floating chat.</t>
+          <t>Image/file usage appears on the Arena ledger for the Local turns.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
@@ -2025,18 +2027,18 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Deploy-modal chat preview matches deployed agent</t>
+          <t>Floating workflow chat streams chart/image</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1. Open deploy modal chat preview for an agent.
-2. Compare theming/welcome behaviour to the live deployed URL.</t>
+          <t>1. Open floating workflow chat.
+2. Run a prompt that produces chart and/or image output.</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Preview matches the deployed agent experience (theme, welcome, basic send).</t>
+          <t>Run streams; chart and image output render in the floating chat.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
@@ -2053,67 +2055,67 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>Workspace chat and Local/Cloud copilot</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Deploy-modal chat preview matches deployed agent</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>1. Open deploy modal chat preview for an agent.
+2. Compare theming/welcome behaviour to the live deployed URL.</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Preview matches the deployed agent experience (theme, welcome, basic send).</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="90" customHeight="1">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>1. Customized — Sim behavior Arena changed</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
           <t>Billing and workspaces</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Credits debit matches ledger after one Agent turn</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>1. Note remaining credits / known balance.
 2. Run one Agent turn.
 3. Compare Usage dashboard debit to the ledger entry (credits-per-dollar).</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>Dashboard debit matches the ledger entry for that turn. No unexplained extra debit.</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43" ht="90" customHeight="1">
-      <c r="A43" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>1. Customized — Sim behavior Arena changed</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Billing and workspaces</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Cost block amount shows once (no double charge)</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>1. Run a workflow with an Agent model cost and an explicit Cost block amount.
-2. Inspect the run’s usage rows.</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Explicit Cost block amount appears once. No double charge vs the Agent model cost.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
@@ -2140,18 +2142,18 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Usage-log multiplier: one scaled ledger row</t>
+          <t>Cost block amount shows once (no double charge)</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1. Run a metered tool that uses the usage-log multiplier.
-2. Inspect ledger rows for that run.</t>
+          <t>1. Run a workflow with an Agent model cost and an explicit Cost block amount.
+2. Inspect the run’s usage rows.</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Exactly one scaled ledger row is written — not a raw row plus a scaled duplicate.</t>
+          <t>Explicit Cost block amount appears once. No double charge vs the Agent model cost.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
@@ -2178,18 +2180,18 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Signup personal workspace; /workspace fallback</t>
+          <t>Usage-log multiplier: one scaled ledger row</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1. Sign up a new user (or use a fresh account path).
-2. Visit /workspace with no id.</t>
+          <t>1. Run a metered tool that uses the usage-log multiplier.
+2. Inspect ledger rows for that run.</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Signup creates a personal workspace. /workspace fallback lands on a valid workspace.</t>
+          <t>Exactly one scaled ledger row is written — not a raw row plus a scaled duplicate.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
@@ -2216,49 +2218,87 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
+          <t>Signup personal workspace; /workspace fallback</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>1. Sign up a new user (or use a fresh account path).
+2. Visit /workspace with no id.</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Signup creates a personal workspace. /workspace fallback lands on a valid workspace.</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47" ht="90" customHeight="1">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>1. Customized — Sim behavior Arena changed</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Billing and workspaces</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
           <t>Daily credit refresh off unless explicitly enabled</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>1. Confirm env does not enable daily refresh (default Arena).
 2. Observe that daily refresh does not run.
 3. If a test env enables it, confirm it then runs.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>Daily refresh stays off by default. It only runs when the environment explicitly enables it.</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr"/>
-      <c r="I46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47" ht="90" customHeight="1">
-      <c r="A47" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48" ht="90" customHeight="1">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>1. Customized — Sim behavior Arena changed</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Billing and workspaces</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>X-Sim-Email bills the named user’s org once</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>1. Open the deploy-modal API sample and confirm X-Sim-Email is present.
 2. Execute the workflow API with X-Sim-Email set to a Sim user in another organization.
@@ -2266,47 +2306,9 @@
 4. Repeat with a missing header, a malformed email, and an email that matches no user.</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>The run bills the named user’s org once. The owning workspace does not also debit it. The billed org’s Usage shows a By Agent row (workflow, owning org · workspace, Run by) and remaining credits drop by that run. A missing header or malformed email is 400. An unknown email is 400 with BILLING_EMAIL_NOT_FOUND.</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr"/>
-      <c r="I47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48" ht="90" customHeight="1">
-      <c r="A48" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>1. Customized — Sim behavior Arena changed</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Workflow engine</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>Response inside loop continues; outside ends</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>1. Build a loop with a Response inside; run.
-2. Build a workflow with a Response outside any loop; run.</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Response inside a loop continues the loop. Response outside a loop ends the workflow.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
@@ -2333,18 +2335,18 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Empty forEach still runs the block after the loop</t>
+          <t>Response inside loop continues; outside ends</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>1. Build a forEach over an empty collection with a successor block after the loop.
-2. Run the workflow.</t>
+          <t>1. Build a loop with a Response inside; run.
+2. Build a workflow with a Response outside any loop; run.</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Loop body is skipped. The block after the loop still executes.</t>
+          <t>Response inside a loop continues the loop. Response outside a loop ends the workflow.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
@@ -2371,18 +2373,18 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Nested loops and nested subflows save and run</t>
+          <t>Empty forEach still runs the block after the loop</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>1. Create nested loops / nested subflows (Arena allows; upstream rejects).
-2. Save and run.</t>
+          <t>1. Build a forEach over an empty collection with a successor block after the loop.
+2. Run the workflow.</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Nested structures save and run successfully.</t>
+          <t>Loop body is skipped. The block after the loop still executes.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
@@ -2409,57 +2411,57 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
+          <t>Nested loops and nested subflows save and run</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>1. Create nested loops / nested subflows (Arena allows; upstream rejects).
+2. Save and run.</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Nested structures save and run successfully.</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52" ht="90" customHeight="1">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>1. Customized — Sim behavior Arena changed</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Workflow engine</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
           <t>Agent model picker: OpenRouter free-only; Azure Anthropic + image models</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>1. Open Agent model picker.
 2. Inspect OpenRouter list pricing.
 3. Confirm Azure Anthropic and Arena-added image models appear where expected.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>OpenRouter list is free-only. Azure Anthropic and Arena image models still appear.</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr"/>
-      <c r="I51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52" ht="90" customHeight="1">
-      <c r="A52" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>1. Customized — Sim behavior Arena changed</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Workflow engine</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>Run logs/console show charts, images, acting user</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>1. Run a workflow that produces chart and image payloads.
-2. Open console and logs for the run.</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>Chart payloads, image payloads, and the acting user are visible in run logs/console.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
@@ -2476,106 +2478,106 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
+          <t>Workflow engine</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Run logs/console show charts, images, acting user</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>1. Run a workflow that produces chart and image payloads.
+2. Open console and logs for the run.</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Chart payloads, image payloads, and the acting user are visible in run logs/console.</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54" ht="90" customHeight="1">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>1. Customized — Sim behavior Arena changed</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
           <t>Extended integrations</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Slack: Arena Bot and Custom Bot, search, post, and Copilot Connect</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>1. In the Slack block, select Arena Bot (bot token) and Custom Bot (user token).
 2. Run Slack search, user-channel lookup, and a normal post.
 3. Ask Copilot to connect Slack while it is disconnected.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>Both auth methods are selectable. Search, lookup, and post each succeed once. Copilot shows one Connect control (“Connect these, then continue”, button Continue), not a Submit button and not a repeated card.</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr"/>
-      <c r="I53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54" ht="90" customHeight="1">
-      <c r="A54" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55" ht="90" customHeight="1">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>1. Customized — Sim behavior Arena changed</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>Extended integrations</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>HubSpot: Accounts picker, campaign op, list contacts</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>1. On an admin workspace, open the HubSpot block and load the Accounts picker.
 2. Select an account and run a read.
 3. Run hubspot_get_campaign_metrics (or another campaign op) and stock hubspot_list_contacts.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>The picker loads real portals and the selected account reads successfully. Campaign op and list contacts both return data.</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55" ht="90" customHeight="1">
-      <c r="A55" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>1. Customized — Sim behavior Arena changed</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Extended integrations</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Google Slides: template tables + stock slide action</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>1. Run create-from-template / template tables (Arena path).
-2. Run one stock slide action.</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>Template tables path and stock slide action each succeed once.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
@@ -2602,18 +2604,18 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Zoom: recordings, transcript download, stock meeting</t>
+          <t>Google Slides: template tables + stock slide action</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>1. Fetch account recordings and download a transcript.
-2. Run one stock meeting action.</t>
+          <t>1. Run create-from-template / template tables (Arena path).
+2. Run one stock slide action.</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Recordings/transcript path and stock meeting action succeed.</t>
+          <t>Template tables path and stock slide action each succeed once.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
@@ -2640,57 +2642,57 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
+          <t>Zoom: recordings, transcript download, stock meeting</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>1. Fetch account recordings and download a transcript.
+2. Run one stock meeting action.</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Recordings/transcript path and stock meeting action succeed.</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58" ht="90" customHeight="1">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>1. Customized — Sim behavior Arena changed</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Extended integrations</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
           <t>Shopify list customers (success) + list products</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Run shopify_list_customers; assert downstream can read success.
 2. Run stock shopify_list_products.
 3. Optionally list/get another resource that previously mapped outputs.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>list_customers succeeds and success remains available downstream. list_products succeeds. Output mapping intact.</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58" ht="90" customHeight="1">
-      <c r="A58" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>1. Customized — Sim behavior Arena changed</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Extended integrations</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>Gmail: advanced search, read thread, send/read</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>1. Run advanced search and read thread.
-2. Send or read a message.</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>Advanced search/thread and send/read each succeed once.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
@@ -2717,18 +2719,18 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Google Drive: upload, AI query helpers, stock file read</t>
+          <t>Gmail: advanced search, read thread, send/read</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>1. Upload a file and run an AI query helper.
-2. Run a stock file read / search.</t>
+          <t>1. Run advanced search and read thread.
+2. Send or read a message.</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Upload, AI query helpers, and stock file read/search succeed.</t>
+          <t>Advanced search/thread and send/read each succeed once.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
@@ -2755,18 +2757,18 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Google Ads v26 search: results consumed as array</t>
+          <t>Google Drive: upload, AI query helpers, stock file read</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>1. Run Google Ads search (GAQL) and confirm the request uses API v26.
-2. Wire a downstream block to results (e.g. forEach or Function).</t>
+          <t>1. Upload a file and run an AI query helper.
+2. Run a stock file read / search.</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Search succeeds on v26. Downstream consumes results as an array (not a bare object / undefined).</t>
+          <t>Upload, AI query helpers, and stock file read/search succeed.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
@@ -2793,96 +2795,96 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
+          <t>Google Ads v26 search: results consumed as array</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>1. Run Google Ads search (GAQL) and confirm the request uses API v26.
+2. Wire a downstream block to results (e.g. forEach or Function).</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Search succeeds on v26. Downstream consumes results as an array (not a bare object / undefined).</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62" ht="90" customHeight="1">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>1. Customized — Sim behavior Arena changed</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Extended integrations</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
           <t>Image Generator: distinct variations, refs, edit</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>1. Prompt “Create 3 distinct variations of …” .
 2. Use a reference image and pick a previously generated image.
 3. Edit that image.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>Three separate images return, not one combined frame. Reference and prior images work. The edit returns an image preview, not an empty or octet-stream file.</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr"/>
-      <c r="I61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62" ht="90" customHeight="1">
-      <c r="A62" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63" ht="90" customHeight="1">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>1. Customized — Sim behavior Arena changed</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>Files</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Generated images/docs open from file serve route</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>1. Generate an image and a compiled document.
 2. Open each via the file serve route.
 3. Reuse a chat image in a later run and open that file.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>Both open from the file serve route. The reused image is copied onto the run and opens. The path is not a broken or context-query URL.</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr"/>
-      <c r="I62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63" ht="90" customHeight="1">
-      <c r="A63" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>1. Customized — Sim behavior Arena changed</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Files</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>Org logo upload and display</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>1. Upload an org logo.
-2. Confirm it displays in the shell/branding surfaces.</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>Logo uploads and displays correctly.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr"/>
@@ -2909,18 +2911,18 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Editor file upload can pick chat images</t>
+          <t>Org logo upload and display</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>1. Generate or attach an image in chat.
-2. From the editor file upload, pick an image already in the chat.</t>
+          <t>1. Upload an org logo.
+2. Confirm it displays in the shell/branding surfaces.</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Editor can select images already present in the chat.</t>
+          <t>Logo uploads and displays correctly.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
@@ -2932,72 +2934,72 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
+          <t>1. Customized — Sim behavior Arena changed</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Editor file upload can pick chat images</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>1. Generate or attach an image in chat.
+2. From the editor file upload, pick an image already in the chat.</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Editor can select images already present in the chat.</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr"/>
+      <c r="I65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66" ht="90" customHeight="1">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>Local copilot runtime</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Tool calls, patches, audit history persist across reload</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. On Local, run a turn that performs tool calls / patches.
 2. Reload the page.
 3. Inspect tool calls, patches, and audit history.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>Tool calls, patches, and audit history persist across reload.</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr"/>
-      <c r="I65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66" ht="90" customHeight="1">
-      <c r="A66" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>2. Exclusive — Arena-only</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Local copilot runtime</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>User access and user memory apply to the next turn</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>1. Configure user access / user memory for Local.
-2. Send a follow-up turn that should use that memory/access.</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>Next turn respects user access and user memory.</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
@@ -3014,67 +3016,67 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
+          <t>Local copilot runtime</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>User access and user memory apply to the next turn</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>1. Configure user access / user memory for Local.
+2. Send a follow-up turn that should use that memory/access.</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Next turn respects user access and user memory.</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68" ht="90" customHeight="1">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>2. Exclusive — Arena-only</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
           <t>Arena task block</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Create task / with fields / sub-task / with fields</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. In the Arena block, run create task.
 2. Create task with fields.
 3. Create sub-task and sub-task with fields.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>All four create operations succeed and return task data.</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr"/>
-      <c r="I67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68" ht="90" customHeight="1">
-      <c r="A68" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>2. Exclusive — Arena-only</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Arena task block</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>Add comment / add comment by task number</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>1. Add a comment on a task.
-2. Add a comment by task number.</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>Both comment operations succeed.</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
@@ -3101,135 +3103,135 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
+          <t>Add comment / add comment by task number</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>1. Add a comment on a task.
+2. Add a comment by task number.</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Both comment operations succeed.</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70" ht="90" customHeight="1">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>2. Exclusive — Arena-only</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Arena task block</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
           <t>Fetch searched tasks / search task / simple search</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Run fetch searched tasks.
 2. Run search task.
 3. Run simple search.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>Each search/fetch operation returns matching task data.</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr"/>
-      <c r="I69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70" ht="90" customHeight="1">
-      <c r="A70" s="2" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71" ht="90" customHeight="1">
+      <c r="A71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>Arena task block</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Save summary / get meetings / get token</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>1. Run save summary.
 2. Run get meetings.
 3. Run get token.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>Each operation succeeds and returns expected payload.</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr"/>
-      <c r="I70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71" ht="90" customHeight="1">
-      <c r="A71" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72" ht="90" customHeight="1">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>Arena task block</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Get my tasks / get my overdue tasks</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. Run get my tasks and get my overdue tasks from the builder.
 2. Start the same workflow from a schedule or a webhook and run both operations again.
 3. If Arena auth fails, confirm the block returns an error.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>Both operations return the user’s tasks from a manual run and from a schedule or webhook run. A failure is an error, not an empty task list.</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr"/>
-      <c r="I71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72" ht="90" customHeight="1">
-      <c r="A72" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>2. Exclusive — Arena-only</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Arena task block</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>Client and project selectors load Arena data</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Arena block panel.
-2. Open client and project selectors.</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>Selectors load real Arena client/project data (not empty stubs / errors).</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr"/>
@@ -3246,28 +3248,28 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Arena Development and generated apps</t>
+          <t>Arena task block</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Arena Development: edit an Arena app</t>
+          <t>Client and project selectors load Arena data</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>1. Add Arena Development block.
-2. Edit an existing Arena app.</t>
+          <t>1. Open the Arena block panel.
+2. Open client and project selectors.</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Edit succeeds and persists for the Arena app.</t>
+          <t>Selectors load real Arena client/project data (not empty stubs / errors).</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr"/>
@@ -3294,57 +3296,57 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
+          <t>Arena Development: edit an Arena app</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>1. Add Arena Development block.
+2. Edit an existing Arena app.</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Edit succeeds and persists for the Arena app.</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75" ht="90" customHeight="1">
+      <c r="A75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>2. Exclusive — Arena-only</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Arena Development and generated apps</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
           <t>Development: generate, edit, deploy to Vercel</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>1. Generate an app with the Development block.
 2. Edit it.
 3. Deploy to Vercel.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>Generate, edit, and Vercel deploy each succeed.</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr"/>
-      <c r="I74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75" ht="90" customHeight="1">
-      <c r="A75" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>2. Exclusive — Arena-only</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Arena Development and generated apps</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>Skill share across workspace/org</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>1. Publish a skill into the catalog.
-2. Use/copy it in another workspace or org.</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>Published skill is usable from the other workspace/org.</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
@@ -3361,7 +3363,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Exclusive blocks</t>
+          <t>Arena Development and generated apps</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -3371,18 +3373,18 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Bing Ads, Facebook Ads, Google Ads V1</t>
+          <t>Skill share across workspace/org</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>1. Confirm each block appears in the block menu.
-2. Run one NL or GAQL/query op per product.</t>
+          <t>1. Publish a skill into the catalog.
+2. Use/copy it in another workspace or org.</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Blocks appear. One operation per product returns data.</t>
+          <t>Published skill is usable from the other workspace/org.</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
@@ -3409,18 +3411,18 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Figma file read or design action</t>
+          <t>Bing Ads, Facebook Ads, Google Ads V1</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>1. Confirm Figma is in the block menu.
-2. Run a file read or design action.</t>
+          <t>1. Confirm each block appears in the block menu.
+2. Run one NL or GAQL/query op per product.</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Block visible; operation returns data.</t>
+          <t>Blocks appear. One operation per product returns data.</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
@@ -3447,18 +3449,18 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Image Fusion</t>
+          <t>Figma file read or design action</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>1. Confirm Image Fusion is in the menu.
-2. Fuse two or more images into one output.</t>
+          <t>1. Confirm Figma is in the block menu.
+2. Run a file read or design action.</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Fused image is produced from multiple inputs.</t>
+          <t>Block visible; operation returns data.</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
@@ -3485,18 +3487,18 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>P2 Docs</t>
+          <t>Image Fusion</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>1. Confirm P2 Docs is in the menu.
-2. Run template schema, icons, or team data once.</t>
+          <t>1. Confirm Image Fusion is in the menu.
+2. Fuse two or more images into one output.</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Block visible; chosen operation returns data.</t>
+          <t>Fused image is produced from multiple inputs.</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr"/>
@@ -3523,18 +3525,18 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Semrush and SpyFu</t>
+          <t>P2 Docs</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>1. Confirm both appear in the menu.
-2. Run one SEO query on each.</t>
+          <t>1. Confirm P2 Docs is in the menu.
+2. Run template schema, icons, or team data once.</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Each returns SEO query data once.</t>
+          <t>Block visible; chosen operation returns data.</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr"/>
@@ -3561,57 +3563,57 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
+          <t>Semrush and SpyFu</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>1. Confirm both appear in the menu.
+2. Run one SEO query on each.</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Each returns SEO query data once.</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82" ht="90" customHeight="1">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>2. Exclusive — Arena-only</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Exclusive blocks</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
           <t>LinkedIn via Unipile</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>1. Confirm Unipile/LinkedIn block is available.
 2. Read company or profile.
 3. Exercise hosted auth / reconnect if needed.</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>Read succeeds. Hosted auth / reconnect works when required.</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr"/>
-      <c r="I81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82" ht="90" customHeight="1">
-      <c r="A82" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>2. Exclusive — Arena-only</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Exclusive blocks</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>Chart Generator</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>1. Confirm Chart Generator is in the menu.
-2. Produce ECharts JSON and render in chat.</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>Chat renderer draws the chart from the JSON output.</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
@@ -3638,18 +3640,18 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Skyvern create or get run</t>
+          <t>Chart Generator</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>1. If credentials exist, create or get a Skyvern run.
-2. Otherwise mark N/A with ticket/env note.</t>
+          <t>1. Confirm Chart Generator is in the menu.
+2. Produce ECharts JSON and render in chat.</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Successful create/get, or explicit N/A with ticket reference when no credential.</t>
+          <t>Chat renderer draws the chart from the JSON output.</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr"/>
@@ -3676,18 +3678,18 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Airweave successful run</t>
+          <t>Skyvern create or get run</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>1. Confirm Airweave visibility for this product build.
-2. Run once, or N/A with ticket if product does not ship it.</t>
+          <t>1. If credentials exist, create or get a Skyvern run.
+2. Otherwise mark N/A with ticket/env note.</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>One successful run, or N/A with ticket reference.</t>
+          <t>Successful create/get, or explicit N/A with ticket reference when no credential.</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
@@ -3704,28 +3706,28 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Deployed-chat extras</t>
+          <t>Exclusive blocks</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Departments, assistant assets, banners, prompt feedback, golden queries</t>
+          <t>Airweave successful run</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>1. Configure/verify departments, assistant assets, banner messages.
-2. Exercise prompt feedback and workflow golden queries on deployed chat.</t>
+          <t>1. Confirm Airweave visibility for this product build.
+2. Run once, or N/A with ticket if product does not ship it.</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>All Arena-only extras render and function; golden queries work with the extras pack.</t>
+          <t>One successful run, or N/A with ticket reference.</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr"/>
@@ -3752,18 +3754,18 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Thread list in left nav; theme sync with Arena shell</t>
+          <t>Departments, assistant assets, banners, prompt feedback, golden queries</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>1. Open deployed chat left nav thread list.
-2. Compare theme with the Arena shell.</t>
+          <t>1. Configure/verify departments, assistant assets, banner messages.
+2. Exercise prompt feedback and workflow golden queries on deployed chat.</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Thread list works. Theme syncs with the Arena shell.</t>
+          <t>All Arena-only extras render and function; golden queries work with the extras pack.</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
@@ -3780,223 +3782,223 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
+          <t>Deployed-chat extras</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Thread list in left nav; theme sync with Arena shell</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>1. Open deployed chat left nav thread list.
+2. Compare theme with the Arena shell.</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Thread list works. Theme syncs with the Arena shell.</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88" ht="90" customHeight="1">
+      <c r="A88" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>2. Exclusive — Arena-only</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
           <t>Admin, identity, and ops</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Arena SSO login, resume, legacy cookie clear</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>1. Log in via Arena SSO.
 2. Resume a session into Sim.
 3. On a user with an old host-only session cookie, sign out/clear and confirm legacy cookies expire.</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>Login and resume work. Legacy session cookies are cleared (including __Secure- / Domain variants).</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr"/>
-      <c r="I87" s="2" t="inlineStr"/>
-    </row>
-    <row r="88" ht="90" customHeight="1">
-      <c r="A88" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89" ht="90" customHeight="1">
+      <c r="A89" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
         <is>
           <t>Admin, identity, and ops</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Custom OAuth apps at org level</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>1. Open Settings → Custom OAuth Apps.
 2. Configure an org-level app with allowed workspaces.
 3. Connect from an allowed workspace; try a disallowed one if applicable.</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>The section shows the apps form, not a blank page. Allowed workspaces can use the app. Restrictions respect org configuration.</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr"/>
-      <c r="I88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89" ht="90" customHeight="1">
-      <c r="A89" s="2" t="n">
-        <v>88</v>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90" ht="90" customHeight="1">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
         <is>
           <t>Admin, identity, and ops</t>
         </is>
       </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Agent access requests</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>1. As a platform-admin email, open Settings → Agent access requests.
 2. Approve one request.
 3. As the requester, open the agents list.</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>The settings page opens. After approval the requester sees that agent enabled.</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr"/>
-      <c r="I89" s="2" t="inlineStr"/>
-    </row>
-    <row r="90" ht="90" customHeight="1">
-      <c r="A90" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91" ht="90" customHeight="1">
+      <c r="A91" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
         <is>
           <t>Agents list and video builder</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Agents list allow-list and undeploy</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>1. With an email on an agent allow-list, open global, shared-with-me, and my-agents.
 2. Repeat with an email outside the list.
 3. Undeploy the chat agent and reload each list. Also confirm an inactive chat is absent.</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>An allowed email sees the agent enabled. An outside email sees it disabled or absent for that tab. Undeploy removes it from all three lists. An inactive chat is not listed.</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr"/>
-      <c r="I90" s="2" t="inlineStr"/>
-    </row>
-    <row r="91" ht="90" customHeight="1">
-      <c r="A91" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92" ht="90" customHeight="1">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
         <is>
           <t>Agents list and video builder</t>
         </is>
       </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Video builder emailId and Fal usage</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>1. From the Arena agents list, open the video builder app while signed in.
 2. Open that same agent detail with emailId omitted, and open a different agent with emailId omitted.
 3. Make a Fal call from the video app and open the Arena user’s usage ledger.</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>The video builder URL has the logged-in email as emailId, replacing any saved email. Omitting emailId still returns the video builder app and rejects every other agent. The Fal call appears on that user’s usage ledger.</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr"/>
-      <c r="I91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92" ht="90" customHeight="1">
-      <c r="A92" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>2. Exclusive — Arena-only</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Admin, identity, and ops</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>Help and support issue filed and stored</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>1. File a help/support issue via the Arena help path.
-2. Confirm it is stored (DB / admin view).</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>Issue is accepted and stored.</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr"/>
@@ -4023,18 +4025,18 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>App banner route and workspace embed page</t>
+          <t>Help and support issue filed and stored</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>1. Open the app banner route inside the host frame.
-2. Open the workspace embed page inside the host frame.</t>
+          <t>1. File a help/support issue via the Arena help path.
+2. Confirm it is stored (DB / admin view).</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Both render correctly inside the host frame.</t>
+          <t>Issue is accepted and stored.</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr"/>
@@ -4061,18 +4063,18 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Default workflows import and deploy for new user</t>
+          <t>App banner route and workspace embed page</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>1. Provision or use a new user.
-2. Confirm default workflows import and can deploy.</t>
+          <t>1. Open the app banner route inside the host frame.
+2. Open the workspace embed page inside the host frame.</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Default workflows import and deploy for the new user.</t>
+          <t>Both render correctly inside the host frame.</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr"/>
@@ -4099,18 +4101,18 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>User knowledge base populate attaches to user</t>
+          <t>Default workflows import and deploy for new user</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>1. Trigger user knowledge base populate.
-2. Confirm attachment to the user.</t>
+          <t>1. Provision or use a new user.
+2. Confirm default workflows import and can deploy.</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>KB populate attaches to the user and is usable afterward.</t>
+          <t>Default workflows import and deploy for the new user.</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr"/>
@@ -4137,10 +4139,48 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
+          <t>User knowledge base populate attaches to user</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>1. Trigger user knowledge base populate.
+2. Confirm attachment to the user.</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>KB populate attaches to the user and is usable afterward.</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr"/>
+      <c r="I96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97" ht="90" customHeight="1">
+      <c r="A97" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>2. Exclusive — Arena-only</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Admin, identity, and ops</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
           <t>Arena general settings (timezone and events)</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>1. Open /workspace/arena-general-settings (no workspace id required).
 2. Save timezone and events.
@@ -4148,47 +4188,9 @@
 4. Spot-check workspace /settings/general still works.</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>Page opens without a workspace id. Timezone/events save and apply to chat and copilot. Workspace general settings unchanged.</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr"/>
-      <c r="I96" s="2" t="inlineStr"/>
-    </row>
-    <row r="97" ht="90" customHeight="1">
-      <c r="A97" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>2. Exclusive — Arena-only</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Billing package (Arena-only)</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>Starter provisioned for a new client org</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>1. Provision a new client org through the Arena path.
-2. Inspect subscription / usage limit.</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>Starter is provisioned with expected usage limit / metadata.</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr"/>
@@ -4215,57 +4217,57 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
+          <t>Starter provisioned for a new client org</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>1. Provision a new client org through the Arena path.
+2. Inspect subscription / usage limit.</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Starter is provisioned with expected usage limit / metadata.</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99" ht="90" customHeight="1">
+      <c r="A99" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>2. Exclusive — Arena-only</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Billing package (Arena-only)</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
           <t>Pro and Max checkout (team_1950 / team_6500)</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>1. As org admin, open upgrade.
 2. Start Pro (team_1950) and/or Max (team_6500) checkout.
 3. Confirm Starter Stripe id is not used for paid checkout.</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>Catalog shows Pro/Max flat org pricing. Checkout ignores Starter Stripe id. Paid checkout can proceed from active Starter.</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr"/>
-      <c r="I98" s="2" t="inlineStr"/>
-    </row>
-    <row r="99" ht="90" customHeight="1">
-      <c r="A99" s="2" t="n">
-        <v>98</v>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>2. Exclusive — Arena-only</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Billing package (Arena-only)</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>Org-admin upgrade comparison overlay</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>1. As org admin, open the upgrade comparison overlay.
-2. Review Starter / Max / Enterprise columns (Pro hidden from comparison table).</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>Overlay shows Arena comparison with flat org pricing copy. Pro is not a comparison column.</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr"/>
@@ -4292,18 +4294,18 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Seat reconcile does not fight flat org pricing</t>
+          <t>Org-admin upgrade comparison overlay</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>1. With an Arena flat org plan, adjust seats / membership.
-2. Observe seat reconcile / pricing behaviour.</t>
+          <t>1. As org admin, open the upgrade comparison overlay.
+2. Review Starter / Max / Enterprise columns (Pro hidden from comparison table).</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Seat reconcile does not multiply or fight flat org pricing.</t>
+          <t>Overlay shows Arena comparison with flat org pricing copy. Pro is not a comparison column.</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr"/>
@@ -4330,18 +4332,18 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Usage limit blocks when exhausted; allows when not</t>
+          <t>Seat reconcile does not fight flat org pricing</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>1. With credits remaining, run a billable action.
-2. Exhaust credits (or use a test org at limit) and retry.</t>
+          <t>1. With an Arena flat org plan, adjust seats / membership.
+2. Observe seat reconcile / pricing behaviour.</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Run allowed under limit. Run blocked when credits are exhausted.</t>
+          <t>Seat reconcile does not multiply or fight flat org pricing.</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr"/>
@@ -4368,18 +4370,18 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Paying supersedes Starter; client-org Starter still provisions</t>
+          <t>Usage limit blocks when exhausted; allows when not</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>1. Confirm a new client org still gets Starter.
-2. Complete paid checkout and verify Starter is superseded.</t>
+          <t>1. With credits remaining, run a billable action.
+2. Exhaust credits (or use a test org at limit) and retry.</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Starter provisioning still runs for client orgs. Paying supersedes Starter.</t>
+          <t>Run allowed under limit. Run blocked when credits are exhausted.</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr"/>
@@ -4391,12 +4393,12 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>3. Other Sim features — stock regression</t>
+          <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Builder core</t>
+          <t>Billing package (Arena-only)</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -4406,18 +4408,18 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Create, rename, duplicate, delete; undo/redo</t>
+          <t>Paying supersedes Starter; client-org Starter still provisions</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>1. Create a workflow; rename; duplicate; delete.
-2. Exercise undo and redo on canvas edits.</t>
+          <t>1. Confirm a new client org still gets Starter.
+2. Complete paid checkout and verify Starter is superseded.</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>CRUD works. Undo/redo restores prior canvas state.</t>
+          <t>Starter provisioning still runs for client orgs. Paying supersedes Starter.</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr"/>
@@ -4444,96 +4446,96 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
+          <t>Create, rename, duplicate, delete; undo/redo</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>1. Create a workflow; rename; duplicate; delete.
+2. Exercise undo and redo on canvas edits.</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>CRUD works. Undo/redo restores prior canvas state.</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr"/>
+      <c r="I104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105" ht="90" customHeight="1">
+      <c r="A105" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>3. Other Sim features — stock regression</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Builder core</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
           <t>Drag blocks, connect edges, editor panel, variables</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>1. Drag blocks onto the canvas and connect edges.
 2. Open the editor panel.
 3. Use a &lt;Block.output&gt; variable reference.</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>Blocks connect. Panel opens. Variables resolve.</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr"/>
-      <c r="I104" s="2" t="inlineStr"/>
-    </row>
-    <row r="105" ht="90" customHeight="1">
-      <c r="A105" s="2" t="n">
-        <v>104</v>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="H105" s="2" t="inlineStr"/>
+      <c r="I105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106" ht="90" customHeight="1">
+      <c r="A106" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>3. Other Sim features — stock regression</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
         <is>
           <t>Builder core</t>
         </is>
       </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Manual run, stop, console; logs page</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>1. Manual run a workflow; stop mid-run if possible.
 2. Read the console.
 3. Open the Logs page for the same run.</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>Run/stop/console work. Logs page shows the same run.</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr"/>
-      <c r="I105" s="2" t="inlineStr"/>
-    </row>
-    <row r="106" ht="90" customHeight="1">
-      <c r="A106" s="2" t="n">
-        <v>105</v>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>3. Other Sim features — stock regression</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Builder core</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>Save/reload; realtime second user</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>1. Save and reload the workflow.
-2. Have a second user open the same workflow and make an edit.</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>State persists after reload. Second user sees realtime updates.</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr"/>
@@ -4560,18 +4562,18 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Deploy; API trigger and chat trigger</t>
+          <t>Save/reload; realtime second user</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>1. Deploy the workflow.
-2. Fire an API trigger and a chat trigger.</t>
+          <t>1. Save and reload the workflow.
+2. Have a second user open the same workflow and make an edit.</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Each trigger starts a run successfully.</t>
+          <t>State persists after reload. Second user sees realtime updates.</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr"/>
@@ -4598,18 +4600,18 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Schedule trigger and webhook trigger</t>
+          <t>Deploy; API trigger and chat trigger</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>1. Configure a schedule; wait for one fire (or advance in test env).
-2. Send one signed webhook request.</t>
+          <t>1. Deploy the workflow.
+2. Fire an API trigger and a chat trigger.</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Schedule fires once. Webhook accepts the signed request and starts a run.</t>
+          <t>Each trigger starts a run successfully.</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr"/>
@@ -4636,18 +4638,18 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Response body; Condition and Router branches</t>
+          <t>Schedule trigger and webhook trigger</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>1. Configure a Response block body and run.
-2. Configure Condition and Router; take each branch once.</t>
+          <t>1. Configure a schedule; wait for one fire (or advance in test env).
+2. Send one signed webhook request.</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Response returns configured body. Condition and Router take the correct branch.</t>
+          <t>Schedule fires once. Webhook accepts the signed request and starts a run.</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr"/>
@@ -4674,56 +4676,57 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
+          <t>Response body; Condition and Router branches</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>1. Configure a Response block body and run.
+2. Configure Condition and Router; take each branch once.</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>Response returns configured body. Condition and Router take the correct branch.</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111" ht="90" customHeight="1">
+      <c r="A111" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>3. Other Sim features — stock regression</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Builder core</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
           <t>Loop and parallel small inner graph</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>1. Run a small loop inner graph.
 2. Run a small parallel inner graph.
 3. (Nested Arena case already covered in section 1.)</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t>Loop and parallel each run the inner graph correctly.</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr"/>
-      <c r="I110" s="2" t="inlineStr"/>
-    </row>
-    <row r="111" ht="90" customHeight="1">
-      <c r="A111" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>3. Other Sim features — stock regression</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>Workspace surfaces</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>Home, workflow list, sidebar navigation</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>1. Open home, workflow list, and navigate the sidebar.</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>All surfaces load and navigate without errors.</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr"/>
@@ -4750,56 +4753,56 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
+          <t>Home, workflow list, sidebar navigation</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>1. Open home, workflow list, and navigate the sidebar.</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>All surfaces load and navigate without errors.</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr"/>
+      <c r="I112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113" ht="90" customHeight="1">
+      <c r="A113" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>3. Other Sim features — stock regression</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Workspace surfaces</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
           <t>Knowledge: create base, upload, retrieve from Agent</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>1. Create a knowledge base; upload a document.
 2. Retrieve it from an Agent block.
 3. Run a search that hits and a search that matches nothing.</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t>Upload succeeds. Agent retrieval returns the document content/citations. A hit includes rank. An empty search returns an empty result the Agent can consume, with no crash on a missing rank.</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr"/>
-      <c r="I112" s="2" t="inlineStr"/>
-    </row>
-    <row r="113" ht="90" customHeight="1">
-      <c r="A113" s="2" t="n">
-        <v>112</v>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>3. Other Sim features — stock regression</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>Workspace surfaces</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr">
-        <is>
-          <t>Tables: create, add row, filter</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>1. Create a table; add a row; apply a filter.</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t>Row appears and filter returns the expected subset.</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr"/>
@@ -4826,18 +4829,17 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Files: upload, preview PDF/image, delete</t>
+          <t>Tables: create, add row, filter</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>1. Upload a PDF and an image.
-2. Preview each; delete one.</t>
+          <t>1. Create a table; add a row; apply a filter.</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Upload/preview/delete succeed for PDF and image.</t>
+          <t>Row appears and filter returns the expected subset.</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr"/>
@@ -4864,18 +4866,18 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Skills: create and attach to agent</t>
+          <t>Files: upload, preview PDF/image, delete</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>1. Create a skill.
-2. Attach it to an agent and run once.</t>
+          <t>1. Upload a PDF and an image.
+2. Preview each; delete one.</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Skill attaches and is used by the agent run.</t>
+          <t>Upload/preview/delete succeed for PDF and image.</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr"/>
@@ -4902,17 +4904,18 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Logs, tests, dashboards, changelog pages load</t>
+          <t>Skills: create and attach to agent</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>1. Open logs, tests, dashboards, and changelog pages.</t>
+          <t>1. Create a skill.
+2. Attach it to an agent and run once.</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Each page loads without error.</t>
+          <t>Skill attaches and is used by the agent run.</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr"/>
@@ -4939,18 +4942,17 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Integrations catalog and connected credential</t>
+          <t>Logs, tests, dashboards, changelog pages load</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>1. Open the integrations catalog.
-2. Open a connected credential detail.</t>
+          <t>1. Open logs, tests, dashboards, and changelog pages.</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Catalog and credential detail both open.</t>
+          <t>Each page loads without error.</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr"/>
@@ -4977,18 +4979,18 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Recently deleted: restore one workflow</t>
+          <t>Integrations catalog and connected credential</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>1. Delete a workflow.
-2. Restore it from Recently deleted.</t>
+          <t>1. Open the integrations catalog.
+2. Open a connected credential detail.</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Workflow restores and opens.</t>
+          <t>Catalog and credential detail both open.</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr"/>
@@ -5005,7 +5007,7 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Workspace surfaces</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -5015,17 +5017,18 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Account, teammates, org members, secrets, credential groups</t>
+          <t>Recently deleted: restore one workflow</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>1. Open each settings page and perform a trivial save/view.</t>
+          <t>1. Delete a workflow.
+2. Restore it from Recently deleted.</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Each page loads; trivial actions succeed.</t>
+          <t>Workflow restores and opens.</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr"/>
@@ -5052,57 +5055,56 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
+          <t>Account, teammates, org members, secrets, credential groups</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>1. Open each settings page and perform a trivial save/view.</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>Each page loads; trivial actions succeed.</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr"/>
+      <c r="I120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121" ht="90" customHeight="1">
+      <c r="A121" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>3. Other Sim features — stock regression</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
           <t>Arena API keys: create, use on API trigger, revoke</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>1. Create an Arena API key.
 2. Use it on an API trigger.
 3. Revoke it and confirm rejection.</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr">
         <is>
           <t>Create/use succeed. After revoke, the key is rejected.</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr"/>
-      <c r="I120" s="2" t="inlineStr"/>
-    </row>
-    <row r="121" ht="90" customHeight="1">
-      <c r="A121" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>3. Other Sim features — stock regression</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>Settings</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E121" s="2" t="inlineStr">
-        <is>
-          <t>Custom tools, MCP tools, MCP servers, sandboxes</t>
-        </is>
-      </c>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>1. Open each settings surface.
-2. Spot-check one create/connect action if credentials allow.</t>
-        </is>
-      </c>
-      <c r="G121" s="2" t="inlineStr">
-        <is>
-          <t>Surfaces load; spot-check action succeeds or is N/A with reason.</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr"/>
@@ -5129,18 +5131,18 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Permission groups and audit logs (enterprise)</t>
+          <t>Custom tools, MCP tools, MCP servers, sandboxes</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>1. If the org has enterprise, open permission groups and audit logs.
-2. Otherwise mark N/A.</t>
+          <t>1. Open each settings surface.
+2. Spot-check one create/connect action if credentials allow.</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Pages load for enterprise orgs; N/A otherwise.</t>
+          <t>Surfaces load; spot-check action succeeds or is N/A with reason.</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr"/>
@@ -5167,18 +5169,18 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Subscription page matches Arena plan</t>
+          <t>Permission groups and audit logs (enterprise)</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>1. Open the subscription page.
-2. Compare to the Arena plan verified in section 2 billing.</t>
+          <t>1. If the org has enterprise, open permission groups and audit logs.
+2. Otherwise mark N/A.</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Subscription page matches the Arena plan (Starter/Pro/Max).</t>
+          <t>Pages load for enterprise orgs; N/A otherwise.</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr"/>
@@ -5195,28 +5197,28 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Agent and model path</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Agent block calls allowed model and returns text</t>
+          <t>Subscription page matches Arena plan</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>1. Configure an Agent block with one allowed model.
-2. Run and read the text output.</t>
+          <t>1. Open the subscription page.
+2. Compare to the Arena plan verified in section 2 billing.</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Agent returns text from the allowed model.</t>
+          <t>Subscription page matches the Arena plan (Starter/Pro/Max).</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr"/>
@@ -5243,18 +5245,18 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Tools the agent calls show in the trace</t>
+          <t>Agent block calls allowed model and returns text</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>1. Run an Agent that calls at least one tool.
-2. Inspect the run trace.</t>
+          <t>1. Configure an Agent block with one allowed model.
+2. Run and read the text output.</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Tool calls appear in the trace.</t>
+          <t>Agent returns text from the allowed model.</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr"/>
@@ -5281,18 +5283,18 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Memory survives a second run in the same thread</t>
+          <t>Tools the agent calls show in the trace</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>1. Run an Agent with memory in a thread.
-2. Run a second turn in the same thread that depends on memory.</t>
+          <t>1. Run an Agent that calls at least one tool.
+2. Inspect the run trace.</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Second run uses memory from the first.</t>
+          <t>Tool calls appear in the trace.</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr"/>
@@ -5309,28 +5311,28 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Representative stock integrations</t>
+          <t>Agent and model path</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Google: Calendar, Sheets, Docs (Gmail/Drive covered in §1)</t>
+          <t>Memory survives a second run in the same thread</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>1. If credentials exist, run one read/write each for Calendar, Sheets, Docs.
-2. Skip Gmail/Drive here if already passed in section 1 Extended; note in Notes.</t>
+          <t>1. Run an Agent with memory in a thread.
+2. Run a second turn in the same thread that depends on memory.</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Each tested Google service succeeds once, or N/A with credential note. Gmail/Drive may be N/A-if-covered-in-§1.</t>
+          <t>Second run uses memory from the first.</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr"/>
@@ -5357,17 +5359,18 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Microsoft: Outlook, Teams, OneDrive</t>
+          <t>Google: Calendar, Sheets, Docs (Gmail/Drive covered in §1)</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>1. With a test account, run one read or write each.</t>
+          <t>1. If credentials exist, run one read/write each for Calendar, Sheets, Docs.
+2. Skip Gmail/Drive here if already passed in section 1 Extended; note in Notes.</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Each succeeds once, or N/A if no credential.</t>
+          <t>Each tested Google service succeeds once, or N/A with credential note. Gmail/Drive may be N/A-if-covered-in-§1.</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr"/>
@@ -5394,12 +5397,12 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Atlassian: Jira, Confluence</t>
+          <t>Microsoft: Outlook, Teams, OneDrive</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>1. Run one Jira and one Confluence happy path.</t>
+          <t>1. With a test account, run one read or write each.</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -5431,13 +5434,12 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Dev: GitHub, Linear (or Jira if Linear unavailable)</t>
+          <t>Atlassian: Jira, Confluence</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>1. Run one GitHub action.
-2. Run one Linear or Jira action.</t>
+          <t>1. Run one Jira and one Confluence happy path.</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -5469,18 +5471,18 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Comms: Discord and Microsoft Teams (Slack covered in §1)</t>
+          <t>Dev: GitHub, Linear (or Jira if Linear unavailable)</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>1. Run Discord and Teams stock ops.
-2. Mark Slack N/A if already covered by section 1 Extended Slack.</t>
+          <t>1. Run one GitHub action.
+2. Run one Linear or Jira action.</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Discord/Teams succeed once, or N/A. Slack noted as covered in §1 when applicable.</t>
+          <t>Each succeeds once, or N/A if no credential.</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr"/>
@@ -5507,18 +5509,18 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>CRM: Salesforce stock read (HubSpot covered in §1)</t>
+          <t>Comms: Discord and Microsoft Teams (Slack covered in §1)</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>1. Run a Salesforce stock read if credentialed.
-2. Mark HubSpot N/A if already covered in section 1.</t>
+          <t>1. Run Discord and Teams stock ops.
+2. Mark Slack N/A if already covered by section 1 Extended Slack.</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Salesforce succeeds once, or N/A. HubSpot noted as covered in §1 when applicable.</t>
+          <t>Discord/Teams succeed once, or N/A. Slack noted as covered in §1 when applicable.</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr"/>
@@ -5545,18 +5547,18 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Data: Airtable or Notion; Postgres or built-in table</t>
+          <t>CRM: Salesforce stock read (HubSpot covered in §1)</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>1. Run one Airtable or Notion op.
-2. Run one Postgres or built-in table op.</t>
+          <t>1. Run a Salesforce stock read if credentialed.
+2. Mark HubSpot N/A if already covered in section 1.</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Each chosen path succeeds once, or N/A if no credential.</t>
+          <t>Salesforce succeeds once, or N/A. HubSpot noted as covered in §1 when applicable.</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr"/>
@@ -5583,17 +5585,18 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>AI utilities: Search, Function, API block, Evaluator</t>
+          <t>Data: Airtable or Notion; Postgres or built-in table</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>1. Run one happy path each for Search, Function, API block, Evaluator.</t>
+          <t>1. Run one Airtable or Notion op.
+2. Run one Postgres or built-in table op.</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>All four succeed once.</t>
+          <t>Each chosen path succeeds once, or N/A if no credential.</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr"/>
@@ -5610,28 +5613,27 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Auth and tenancy</t>
+          <t>Representative stock integrations</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Email sign-in and sign-out; invite and accept</t>
+          <t>AI utilities: Search, Function, API block, Evaluator</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>1. Sign in with email; sign out.
-2. Invite a member and accept the invite.</t>
+          <t>1. Run one happy path each for Search, Function, API block, Evaluator.</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Sign-in/out work. Invite accept grants membership.</t>
+          <t>All four succeed once.</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr"/>
@@ -5658,17 +5660,18 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Member cannot open another org’s workspace</t>
+          <t>Email sign-in and sign-out; invite and accept</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>1. As a member of org A, attempt to open org B’s workspace URL.</t>
+          <t>1. Sign in with email; sign out.
+2. Invite a member and accept the invite.</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Access is denied; workspace from another org is not opened.</t>
+          <t>Sign-in/out work. Invite accept grants membership.</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr"/>
@@ -5695,18 +5698,17 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Archived workspace is not selectable</t>
+          <t>Member cannot open another org’s workspace</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>1. Archive a workspace (or use a known archived one).
-2. Try to select it from the workspace picker.</t>
+          <t>1. As a member of org A, attempt to open org B’s workspace URL.</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Archived workspace is not selectable.</t>
+          <t>Access is denied; workspace from another org is not opened.</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr"/>
@@ -5733,27 +5735,65 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
+          <t>Archived workspace is not selectable</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>1. Archive a workspace (or use a known archived one).
+2. Try to select it from the workspace picker.</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>Archived workspace is not selectable.</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr"/>
+      <c r="I138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139" ht="90" customHeight="1">
+      <c r="A139" s="2" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>3. Other Sim features — stock regression</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Auth and tenancy</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
           <t>API key from another workspace is rejected</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>1. Take an API key from workspace A.
 2. Call a protected API scoped to workspace B.</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr">
         <is>
           <t>Request is rejected (unauthorized / wrong workspace).</t>
         </is>
       </c>
-      <c r="H138" s="2" t="inlineStr"/>
-      <c r="I138" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr"/>
+      <c r="I139" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I138"/>
+  <autoFilter ref="A1:I139"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H138" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid result" error="Choose Pass, Fail, or N/A" type="list">
+    <dataValidation sqref="H2:H139" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid result" error="Choose Pass, Fail, or N/A" type="list">
       <formula1>"Pass,Fail,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5929,7 +5969,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kept rows: 137 (P0=77, P1=39, P2=21)</t>
+          <t>Kept rows: 138 (P0=78, P1=39, P2=21)</t>
         </is>
       </c>
     </row>
